--- a/model/Outputs/11. Interest rate/0/Output Files/0.2/Output_12_36.xlsx
+++ b/model/Outputs/11. Interest rate/0/Output Files/0.2/Output_12_36.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2212823.449348561</v>
+        <v>2213894.573060836</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14697842.82031956</v>
+        <v>14697842.82031957</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14697842.82031956</v>
+        <v>14697842.82031957</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>657188.6984941054</v>
+        <v>657188.6984941055</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>657188.6984941054</v>
+        <v>657188.6984941055</v>
       </c>
     </row>
     <row r="11">
@@ -672,10 +672,10 @@
         <v>3.34732203575993</v>
       </c>
       <c r="H2" t="n">
-        <v>5.608919435675552</v>
+        <v>3.81023156784903</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1.79868786782652</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -748,13 +748,13 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>325.5201396486123</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>8.970794211717337</v>
       </c>
       <c r="I3" t="n">
-        <v>209.5726123064429</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
         <v>145.073529241423</v>
       </c>
       <c r="R3" t="n">
-        <v>374</v>
+        <v>133.6519859716245</v>
       </c>
       <c r="S3" t="n">
         <v>62.48881128536601</v>
       </c>
       <c r="T3" t="n">
+        <v>4.473444462796863</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.1959257979225981</v>
+      </c>
+      <c r="V3" t="n">
         <v>374</v>
       </c>
-      <c r="U3" t="n">
-        <v>216.355867684882</v>
-      </c>
-      <c r="V3" t="n">
-        <v>14.51066719152016</v>
-      </c>
       <c r="W3" t="n">
-        <v>32.37314290982852</v>
+        <v>374</v>
       </c>
       <c r="X3" t="n">
         <v>19.86273944538755</v>
@@ -909,7 +909,7 @@
         <v>3.34732203575993</v>
       </c>
       <c r="H5" t="n">
-        <v>3.81023156784903</v>
+        <v>5.608919435675552</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -942,7 +942,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>87.30283556964716</v>
+        <v>85.50414770182039</v>
       </c>
       <c r="T5" t="n">
         <v>184.8805867536895</v>
@@ -970,10 +970,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>300.5072113134616</v>
+        <v>374</v>
       </c>
       <c r="C6" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -991,7 +991,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>209.5726123064429</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1018,7 +1018,7 @@
         <v>145.073529241423</v>
       </c>
       <c r="R6" t="n">
-        <v>133.6519859716245</v>
+        <v>231.54923686955</v>
       </c>
       <c r="S6" t="n">
         <v>62.48881128536601</v>
@@ -1036,10 +1036,10 @@
         <v>32.37314290982852</v>
       </c>
       <c r="X6" t="n">
-        <v>19.86273944538755</v>
+        <v>374</v>
       </c>
       <c r="Y6" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1176,10 +1176,10 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.798687867826661</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>85.50414770182039</v>
+        <v>87.30283556964716</v>
       </c>
       <c r="T8" t="n">
         <v>184.8805867536895</v>
@@ -1207,64 +1207,64 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>209.5726123064429</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
         <v>374</v>
       </c>
-      <c r="C9" t="n">
-        <v>361.0999124455193</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>71.58074055488474</v>
-      </c>
-      <c r="R9" t="n">
-        <v>133.6519859716245</v>
-      </c>
       <c r="S9" t="n">
-        <v>62.48881128536601</v>
+        <v>374</v>
       </c>
       <c r="T9" t="n">
-        <v>4.473444462796863</v>
+        <v>374</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1959257979225981</v>
+        <v>49.9182082116711</v>
       </c>
       <c r="V9" t="n">
         <v>14.51066719152016</v>
@@ -1276,7 +1276,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y9" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>162.3032279590796</v>
+        <v>162.9993129555745</v>
       </c>
       <c r="C11" t="n">
         <v>130.4745782429939</v>
@@ -1380,10 +1380,10 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G11" t="n">
-        <v>83.28199540259408</v>
+        <v>83.28199540259411</v>
       </c>
       <c r="H11" t="n">
-        <v>73.89995518593946</v>
+        <v>73.20387018944457</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1450,19 +1450,19 @@
         <v>42.09991244551929</v>
       </c>
       <c r="D12" t="n">
-        <v>347.9376868977026</v>
+        <v>28.93768689770263</v>
       </c>
       <c r="E12" t="n">
         <v>23.67209722191262</v>
       </c>
       <c r="F12" t="n">
-        <v>339.6362423378769</v>
+        <v>20.63624233787687</v>
       </c>
       <c r="G12" t="n">
-        <v>228.8924124088879</v>
+        <v>5.950139648612248</v>
       </c>
       <c r="H12" t="n">
-        <v>5.544181526043758</v>
+        <v>5.544181526043773</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1489,28 +1489,28 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>72.31352924142297</v>
       </c>
       <c r="R12" t="n">
-        <v>179.2619859716245</v>
+        <v>498.2619859716245</v>
       </c>
       <c r="S12" t="n">
-        <v>132.901311285366</v>
+        <v>283.5300548042187</v>
       </c>
       <c r="T12" t="n">
-        <v>83.17594446279685</v>
+        <v>402.1759444627968</v>
       </c>
       <c r="U12" t="n">
-        <v>81.15842579792258</v>
+        <v>81.1584257979226</v>
       </c>
       <c r="V12" t="n">
         <v>95.51066719152016</v>
       </c>
       <c r="W12" t="n">
-        <v>432.3731429098285</v>
+        <v>113.3731429098285</v>
       </c>
       <c r="X12" t="n">
-        <v>100.8627394453875</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y12" t="n">
         <v>80.39139276613435</v>
@@ -1553,13 +1553,13 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>6.155529797123449</v>
+        <v>6.155529797123435</v>
       </c>
       <c r="M13" t="n">
-        <v>97.89093927140237</v>
+        <v>97.89093927140236</v>
       </c>
       <c r="N13" t="n">
-        <v>150.9111244520127</v>
+        <v>148.0607629745462</v>
       </c>
       <c r="O13" t="n">
         <v>227.9026788331133</v>
@@ -1568,13 +1568,13 @@
         <v>288.4057989676218</v>
       </c>
       <c r="Q13" t="n">
-        <v>348.5719049481316</v>
+        <v>351.422266425598</v>
       </c>
       <c r="R13" t="n">
-        <v>377.8450460139379</v>
+        <v>377.845046013938</v>
       </c>
       <c r="S13" t="n">
-        <v>31.84005347334727</v>
+        <v>31.84005347334724</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1617,10 +1617,10 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G14" t="n">
-        <v>83.28199540259408</v>
+        <v>83.28199540259411</v>
       </c>
       <c r="H14" t="n">
-        <v>73.89995518593946</v>
+        <v>73.89995518593948</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1653,13 +1653,13 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>142.2280170485541</v>
+        <v>141.5319320520589</v>
       </c>
       <c r="T14" t="n">
         <v>261.2171194170061</v>
       </c>
       <c r="U14" t="n">
-        <v>329.4071814013618</v>
+        <v>330.1032663978569</v>
       </c>
       <c r="V14" t="n">
         <v>310.8510241668239</v>
@@ -1684,10 +1684,10 @@
         <v>65.55655664632661</v>
       </c>
       <c r="C15" t="n">
-        <v>361.0999124455193</v>
+        <v>42.09991244551929</v>
       </c>
       <c r="D15" t="n">
-        <v>251.8799596579781</v>
+        <v>28.93768689770263</v>
       </c>
       <c r="E15" t="n">
         <v>23.67209722191262</v>
@@ -1696,10 +1696,10 @@
         <v>20.63624233787687</v>
       </c>
       <c r="G15" t="n">
-        <v>5.950139648612264</v>
+        <v>5.950139648612248</v>
       </c>
       <c r="H15" t="n">
-        <v>5.544181526043758</v>
+        <v>5.544181526043773</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1729,22 +1729,22 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>179.2619859716245</v>
+        <v>179.2619859716246</v>
       </c>
       <c r="S15" t="n">
         <v>132.901311285366</v>
       </c>
       <c r="T15" t="n">
-        <v>83.17594446279685</v>
+        <v>83.17594446279683</v>
       </c>
       <c r="U15" t="n">
-        <v>81.15842579792258</v>
+        <v>304.1006985581982</v>
       </c>
       <c r="V15" t="n">
         <v>414.5106671915202</v>
       </c>
       <c r="W15" t="n">
-        <v>113.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X15" t="n">
         <v>419.8627394453875</v>
@@ -1790,10 +1790,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>6.155529797123449</v>
+        <v>6.155529797123435</v>
       </c>
       <c r="M16" t="n">
-        <v>97.89093927140237</v>
+        <v>97.89093927140236</v>
       </c>
       <c r="N16" t="n">
         <v>150.9111244520127</v>
@@ -1805,13 +1805,13 @@
         <v>288.4057989676218</v>
       </c>
       <c r="Q16" t="n">
-        <v>351.422266425598</v>
+        <v>348.5719049481316</v>
       </c>
       <c r="R16" t="n">
-        <v>377.8450460139379</v>
+        <v>377.845046013938</v>
       </c>
       <c r="S16" t="n">
-        <v>28.98969199588095</v>
+        <v>31.84005347334724</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>142.2280170485541</v>
+        <v>141.5319320520589</v>
       </c>
       <c r="T17" t="n">
         <v>261.2171194170061</v>
@@ -1905,7 +1905,7 @@
         <v>319.3734759809475</v>
       </c>
       <c r="X17" t="n">
-        <v>272.5857484641728</v>
+        <v>273.2818334606677</v>
       </c>
       <c r="Y17" t="n">
         <v>192.3174326828064</v>
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>65.55655664632661</v>
+        <v>288.4988294066023</v>
       </c>
       <c r="C18" t="n">
         <v>42.09991244551929</v>
@@ -1978,7 +1978,7 @@
         <v>81.15842579792258</v>
       </c>
       <c r="V18" t="n">
-        <v>414.5106671915202</v>
+        <v>95.51066719152016</v>
       </c>
       <c r="W18" t="n">
         <v>432.3731429098285</v>
@@ -1987,7 +1987,7 @@
         <v>419.8627394453875</v>
       </c>
       <c r="Y18" t="n">
-        <v>303.3336655264099</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="19">
@@ -2085,7 +2085,7 @@
         <v>91.33915573984979</v>
       </c>
       <c r="E20" t="n">
-        <v>85.36328960686865</v>
+        <v>84.66720461037373</v>
       </c>
       <c r="F20" t="n">
         <v>85.88962870801186</v>
@@ -2127,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>141.5319320520589</v>
+        <v>142.2280170485541</v>
       </c>
       <c r="T20" t="n">
         <v>261.2171194170061</v>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>288.4988294066021</v>
+        <v>65.55655664632661</v>
       </c>
       <c r="C21" t="n">
-        <v>361.0999124455193</v>
+        <v>42.09991244551929</v>
       </c>
       <c r="D21" t="n">
         <v>347.9376868977026</v>
@@ -2167,13 +2167,13 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F21" t="n">
-        <v>20.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G21" t="n">
         <v>5.950139648612264</v>
       </c>
       <c r="H21" t="n">
-        <v>5.544181526043758</v>
+        <v>228.4864542863195</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2328,7 +2328,7 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G23" t="n">
-        <v>83.28199540259411</v>
+        <v>82.58591040609919</v>
       </c>
       <c r="H23" t="n">
         <v>73.89995518593948</v>
@@ -2364,7 +2364,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>141.5319320520589</v>
+        <v>142.2280170485541</v>
       </c>
       <c r="T23" t="n">
         <v>261.2171194170061</v>
@@ -2395,7 +2395,7 @@
         <v>65.55655664632661</v>
       </c>
       <c r="C24" t="n">
-        <v>361.0999124455193</v>
+        <v>265.042185205795</v>
       </c>
       <c r="D24" t="n">
         <v>347.9376868977026</v>
@@ -2404,7 +2404,7 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F24" t="n">
-        <v>243.5785150981525</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G24" t="n">
         <v>5.950139648612248</v>
@@ -2568,7 +2568,7 @@
         <v>82.58591040609919</v>
       </c>
       <c r="H26" t="n">
-        <v>73.89995518593946</v>
+        <v>73.89995518593948</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2638,16 +2638,16 @@
         <v>28.93768689770263</v>
       </c>
       <c r="E27" t="n">
-        <v>342.6720972219126</v>
+        <v>23.67209722191262</v>
       </c>
       <c r="F27" t="n">
-        <v>339.6362423378769</v>
+        <v>20.63624233787687</v>
       </c>
       <c r="G27" t="n">
-        <v>228.8924124088878</v>
+        <v>5.950139648612248</v>
       </c>
       <c r="H27" t="n">
-        <v>5.544181526043758</v>
+        <v>228.4864542863191</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2677,28 +2677,28 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>179.2619859716245</v>
+        <v>179.2619859716246</v>
       </c>
       <c r="S27" t="n">
-        <v>132.901311285366</v>
+        <v>451.901311285366</v>
       </c>
       <c r="T27" t="n">
-        <v>83.17594446279685</v>
+        <v>83.17594446279683</v>
       </c>
       <c r="U27" t="n">
-        <v>81.15842579792258</v>
+        <v>81.1584257979226</v>
       </c>
       <c r="V27" t="n">
-        <v>95.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W27" t="n">
-        <v>113.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X27" t="n">
         <v>100.8627394453875</v>
       </c>
       <c r="Y27" t="n">
-        <v>399.3913927661343</v>
+        <v>80.39139276613435</v>
       </c>
     </row>
     <row r="28">
@@ -2738,10 +2738,10 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>6.155529797123449</v>
+        <v>6.155529797123435</v>
       </c>
       <c r="M28" t="n">
-        <v>97.89093927140237</v>
+        <v>97.89093927140236</v>
       </c>
       <c r="N28" t="n">
         <v>150.9111244520127</v>
@@ -2753,13 +2753,13 @@
         <v>288.4057989676218</v>
       </c>
       <c r="Q28" t="n">
-        <v>348.5719049481316</v>
+        <v>351.422266425598</v>
       </c>
       <c r="R28" t="n">
-        <v>377.8450460139379</v>
+        <v>377.845046013938</v>
       </c>
       <c r="S28" t="n">
-        <v>31.84005347334727</v>
+        <v>28.98969199588089</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2802,10 +2802,10 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G29" t="n">
-        <v>82.58591040609919</v>
+        <v>83.28199540259408</v>
       </c>
       <c r="H29" t="n">
-        <v>73.89995518593948</v>
+        <v>73.89995518593946</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2844,7 +2844,7 @@
         <v>261.2171194170061</v>
       </c>
       <c r="U29" t="n">
-        <v>330.1032663978569</v>
+        <v>329.4071814013618</v>
       </c>
       <c r="V29" t="n">
         <v>310.8510241668239</v>
@@ -2872,7 +2872,7 @@
         <v>42.09991244551929</v>
       </c>
       <c r="D30" t="n">
-        <v>28.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E30" t="n">
         <v>342.6720972219126</v>
@@ -2881,13 +2881,13 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G30" t="n">
-        <v>5.950139648612248</v>
+        <v>5.950139648612264</v>
       </c>
       <c r="H30" t="n">
-        <v>5.544181526043773</v>
+        <v>5.544181526043758</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>189.9476123064429</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2914,28 +2914,28 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>179.2619859716246</v>
+        <v>179.2619859716245</v>
       </c>
       <c r="S30" t="n">
         <v>132.901311285366</v>
       </c>
       <c r="T30" t="n">
-        <v>83.17594446279683</v>
+        <v>83.17594446279685</v>
       </c>
       <c r="U30" t="n">
-        <v>81.1584257979226</v>
+        <v>81.15842579792258</v>
       </c>
       <c r="V30" t="n">
-        <v>318.4529399517957</v>
+        <v>95.51066719152016</v>
       </c>
       <c r="W30" t="n">
         <v>113.3731429098285</v>
       </c>
       <c r="X30" t="n">
-        <v>419.8627394453875</v>
+        <v>100.8627394453875</v>
       </c>
       <c r="Y30" t="n">
-        <v>80.39139276613435</v>
+        <v>113.3860532199671</v>
       </c>
     </row>
     <row r="31">
@@ -2975,10 +2975,10 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>3.305168319656873</v>
+        <v>6.155529797123449</v>
       </c>
       <c r="M31" t="n">
-        <v>97.89093927140236</v>
+        <v>97.89093927140237</v>
       </c>
       <c r="N31" t="n">
         <v>150.9111244520127</v>
@@ -2993,10 +2993,10 @@
         <v>351.422266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>377.845046013938</v>
+        <v>377.8450460139379</v>
       </c>
       <c r="S31" t="n">
-        <v>31.84005347334724</v>
+        <v>28.98969199588095</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3148,31 +3148,31 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>72.31352924142297</v>
       </c>
       <c r="R33" t="n">
-        <v>179.2619859716246</v>
+        <v>498.2619859716245</v>
       </c>
       <c r="S33" t="n">
-        <v>132.901311285366</v>
+        <v>451.901311285366</v>
       </c>
       <c r="T33" t="n">
-        <v>83.17594446279683</v>
+        <v>233.8046879816494</v>
       </c>
       <c r="U33" t="n">
         <v>81.1584257979226</v>
       </c>
       <c r="V33" t="n">
-        <v>414.5106671915202</v>
+        <v>95.51066719152016</v>
       </c>
       <c r="W33" t="n">
-        <v>432.3731429098285</v>
+        <v>113.3731429098285</v>
       </c>
       <c r="X33" t="n">
-        <v>419.8627394453875</v>
+        <v>100.8627394453875</v>
       </c>
       <c r="Y33" t="n">
-        <v>303.3336655264099</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="34">
@@ -3233,7 +3233,7 @@
         <v>377.845046013938</v>
       </c>
       <c r="S34" t="n">
-        <v>28.98969199589125</v>
+        <v>28.98969199588899</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3276,7 +3276,7 @@
         <v>7.889628708011855</v>
       </c>
       <c r="G35" t="n">
-        <v>1.981065592038484</v>
+        <v>5.2819954025941</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -3330,7 +3330,7 @@
         <v>195.2818334606677</v>
       </c>
       <c r="Y35" t="n">
-        <v>114.3174326828064</v>
+        <v>111.0165028722508</v>
       </c>
     </row>
     <row r="36">
@@ -3340,13 +3340,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>374</v>
+        <v>374.0000000000583</v>
       </c>
       <c r="C36" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -3358,7 +3358,7 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>112.0377223807662</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -3406,10 +3406,10 @@
         <v>35.37314290982852</v>
       </c>
       <c r="X36" t="n">
-        <v>22.86273944538755</v>
+        <v>374.0000000000583</v>
       </c>
       <c r="Y36" t="n">
-        <v>128.1373835923317</v>
+        <v>374.0000000000583</v>
       </c>
     </row>
     <row r="37">
@@ -3510,7 +3510,7 @@
         <v>7.363289606868648</v>
       </c>
       <c r="F38" t="n">
-        <v>7.889628708011855</v>
+        <v>4.588698897456261</v>
       </c>
       <c r="G38" t="n">
         <v>5.281995402594077</v>
@@ -3549,7 +3549,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>60.92708723799848</v>
+        <v>64.22801704855408</v>
       </c>
       <c r="T38" t="n">
         <v>183.2171194170061</v>
@@ -3580,16 +3580,16 @@
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>178.5375637119275</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>189.9476123064429</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3622,10 +3622,10 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>72.31352924142297</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>320.4535275826207</v>
+        <v>101.2619859716245</v>
       </c>
       <c r="S39" t="n">
         <v>54.90131128536603</v>
@@ -3634,10 +3634,10 @@
         <v>5.175944462796849</v>
       </c>
       <c r="U39" t="n">
-        <v>374</v>
+        <v>3.158425797922575</v>
       </c>
       <c r="V39" t="n">
-        <v>374</v>
+        <v>17.51066719152016</v>
       </c>
       <c r="W39" t="n">
         <v>35.37314290982852</v>
@@ -3735,19 +3735,19 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>27.91440986465916</v>
       </c>
       <c r="C41" t="n">
         <v>156.4745782429939</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>117.3391557398498</v>
       </c>
       <c r="E41" t="n">
         <v>111.3632896068686</v>
       </c>
       <c r="F41" t="n">
-        <v>111.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -3786,13 +3786,13 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>168.2280170485541</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>221.2391862457997</v>
+        <v>356.1032663978569</v>
       </c>
       <c r="V41" t="n">
         <v>336.8510241668239</v>
@@ -3832,7 +3832,7 @@
         <v>31.95013964861226</v>
       </c>
       <c r="H42" t="n">
-        <v>31.54418152604376</v>
+        <v>33.93095497146885</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -3859,7 +3859,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.386773445425144</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>205.2619859716245</v>
@@ -3923,25 +3923,25 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>32.15552979712345</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>123.8909392714024</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>176.9111244520127</v>
       </c>
       <c r="O43" t="n">
-        <v>1.555623315090222</v>
+        <v>253.9026788331133</v>
       </c>
       <c r="P43" t="n">
         <v>314.4057989676218</v>
       </c>
       <c r="Q43" t="n">
-        <v>374.0000000006313</v>
+        <v>162.6953509620701</v>
       </c>
       <c r="R43" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>57.84005347334727</v>
@@ -3990,7 +3990,7 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>99.89995518593948</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4032,13 +4032,13 @@
         <v>356.1032663978569</v>
       </c>
       <c r="V44" t="n">
-        <v>163.4435047435215</v>
+        <v>336.8510241668239</v>
       </c>
       <c r="W44" t="n">
         <v>345.3734759809475</v>
       </c>
       <c r="X44" t="n">
-        <v>299.2818334606677</v>
+        <v>25.97435885142596</v>
       </c>
       <c r="Y44" t="n">
         <v>0</v>
@@ -4096,10 +4096,10 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.386773445425144</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>205.2619859716246</v>
+        <v>207.6487594170497</v>
       </c>
       <c r="S45" t="n">
         <v>158.901311285366</v>
@@ -4172,13 +4172,13 @@
         <v>253.9026788331133</v>
       </c>
       <c r="P46" t="n">
-        <v>103.1011499288239</v>
+        <v>314.4057989676218</v>
       </c>
       <c r="Q46" t="n">
-        <v>374.0000000008678</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>162.6953509620699</v>
       </c>
       <c r="S46" t="n">
         <v>57.84005347334724</v>
@@ -4315,31 +4315,31 @@
         <v>35.58557518755106</v>
       </c>
       <c r="H2" t="n">
-        <v>29.92</v>
+        <v>31.736856432148</v>
       </c>
       <c r="I2" t="n">
         <v>29.92</v>
       </c>
       <c r="J2" t="n">
-        <v>29.92</v>
+        <v>400.18</v>
       </c>
       <c r="K2" t="n">
-        <v>400.18</v>
+        <v>691.4180850251257</v>
       </c>
       <c r="L2" t="n">
-        <v>770.4399999999999</v>
+        <v>755.48</v>
       </c>
       <c r="M2" t="n">
-        <v>770.4399999999999</v>
+        <v>755.48</v>
       </c>
       <c r="N2" t="n">
+        <v>755.48</v>
+      </c>
+      <c r="O2" t="n">
+        <v>755.48</v>
+      </c>
+      <c r="P2" t="n">
         <v>1125.74</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1125.74</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1496</v>
       </c>
       <c r="Q2" t="n">
         <v>1496</v>
@@ -4376,25 +4376,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>244.8234770117097</v>
+        <v>371.0035997934135</v>
       </c>
       <c r="C3" t="n">
-        <v>244.8234770117097</v>
+        <v>371.0035997934135</v>
       </c>
       <c r="D3" t="n">
-        <v>244.8234770117097</v>
+        <v>371.0035997934135</v>
       </c>
       <c r="E3" t="n">
-        <v>244.8234770117097</v>
+        <v>371.0035997934135</v>
       </c>
       <c r="F3" t="n">
-        <v>244.8234770117097</v>
+        <v>371.0035997934135</v>
       </c>
       <c r="G3" t="n">
-        <v>244.8234770117097</v>
+        <v>42.19537792612834</v>
       </c>
       <c r="H3" t="n">
-        <v>244.8234770117097</v>
+        <v>33.13396963146437</v>
       </c>
       <c r="I3" t="n">
         <v>33.13396963146437</v>
@@ -4424,28 +4424,28 @@
         <v>1349.46108157432</v>
       </c>
       <c r="R3" t="n">
-        <v>971.6833037965423</v>
+        <v>1214.459075542376</v>
       </c>
       <c r="S3" t="n">
-        <v>908.5632923971827</v>
+        <v>1151.339064143017</v>
       </c>
       <c r="T3" t="n">
-        <v>530.7855146194049</v>
+        <v>1146.820433372515</v>
       </c>
       <c r="U3" t="n">
-        <v>312.2442341296251</v>
+        <v>1146.622528526128</v>
       </c>
       <c r="V3" t="n">
-        <v>297.586994542231</v>
+        <v>768.8447507483504</v>
       </c>
       <c r="W3" t="n">
-        <v>264.8868501888688</v>
+        <v>391.0669729705726</v>
       </c>
       <c r="X3" t="n">
-        <v>244.8234770117097</v>
+        <v>371.0035997934135</v>
       </c>
       <c r="Y3" t="n">
-        <v>244.8234770117097</v>
+        <v>371.0035997934135</v>
       </c>
     </row>
     <row r="4">
@@ -4455,34 +4455,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>444.5411051194287</v>
+        <v>465.4012323549126</v>
       </c>
       <c r="C4" t="n">
-        <v>489.8389515573086</v>
+        <v>591.4032381733484</v>
       </c>
       <c r="D4" t="n">
-        <v>603.1580956823087</v>
+        <v>704.7223822983485</v>
       </c>
       <c r="E4" t="n">
-        <v>720.9869998937218</v>
+        <v>822.5512865097616</v>
       </c>
       <c r="F4" t="n">
-        <v>845.3479724856572</v>
+        <v>946.912259101697</v>
       </c>
       <c r="G4" t="n">
-        <v>845.3479724856572</v>
+        <v>946.912259101697</v>
       </c>
       <c r="H4" t="n">
-        <v>1016.483548464727</v>
+        <v>1118.047835080767</v>
       </c>
       <c r="I4" t="n">
-        <v>1016.483548464727</v>
+        <v>1118.047835080767</v>
       </c>
       <c r="J4" t="n">
-        <v>1386.743548464727</v>
+        <v>1382.983127881912</v>
       </c>
       <c r="K4" t="n">
-        <v>1386.743548464727</v>
+        <v>1382.983127881912</v>
       </c>
       <c r="L4" t="n">
         <v>1386.743548464727</v>
@@ -4518,13 +4518,13 @@
         <v>70.34367574991084</v>
       </c>
       <c r="W4" t="n">
-        <v>70.34367574991084</v>
+        <v>242.2345940095882</v>
       </c>
       <c r="X4" t="n">
-        <v>221.3744667741043</v>
+        <v>242.2345940095882</v>
       </c>
       <c r="Y4" t="n">
-        <v>332.7837674531366</v>
+        <v>353.6438946886205</v>
       </c>
     </row>
     <row r="5">
@@ -4534,22 +4534,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>106.914147375084</v>
+        <v>108.731003807232</v>
       </c>
       <c r="C5" t="n">
-        <v>56.9398259175144</v>
+        <v>58.7566823496624</v>
       </c>
       <c r="D5" t="n">
-        <v>46.49623426110047</v>
+        <v>48.31309069324847</v>
       </c>
       <c r="E5" t="n">
-        <v>42.08887102183921</v>
+        <v>43.90572745398721</v>
       </c>
       <c r="F5" t="n">
-        <v>37.14985212485754</v>
+        <v>38.96670855700554</v>
       </c>
       <c r="G5" t="n">
-        <v>33.76871875540306</v>
+        <v>35.58557518755106</v>
       </c>
       <c r="H5" t="n">
         <v>29.92</v>
@@ -4561,22 +4561,22 @@
         <v>400.18</v>
       </c>
       <c r="K5" t="n">
-        <v>770.4399999999999</v>
+        <v>451.8183303517587</v>
       </c>
       <c r="L5" t="n">
-        <v>1067.648108133742</v>
+        <v>515.8802453266331</v>
       </c>
       <c r="M5" t="n">
-        <v>1067.648108133742</v>
+        <v>886.1402453266331</v>
       </c>
       <c r="N5" t="n">
-        <v>1067.648108133742</v>
+        <v>886.1402453266331</v>
       </c>
       <c r="O5" t="n">
-        <v>1067.648108133742</v>
+        <v>1256.400245326633</v>
       </c>
       <c r="P5" t="n">
-        <v>1125.74</v>
+        <v>1314.492137192891</v>
       </c>
       <c r="Q5" t="n">
         <v>1496</v>
@@ -4585,25 +4585,25 @@
         <v>1496</v>
       </c>
       <c r="S5" t="n">
-        <v>1407.815317606417</v>
+        <v>1409.632174038565</v>
       </c>
       <c r="T5" t="n">
-        <v>1221.067250178448</v>
+        <v>1222.884106610596</v>
       </c>
       <c r="U5" t="n">
-        <v>969.3617021698518</v>
+        <v>971.1785586019998</v>
       </c>
       <c r="V5" t="n">
-        <v>737.1889504861913</v>
+        <v>739.0058069183393</v>
       </c>
       <c r="W5" t="n">
-        <v>496.4076616165473</v>
+        <v>498.2245180486953</v>
       </c>
       <c r="X5" t="n">
-        <v>302.1835874138526</v>
+        <v>304.0004438460006</v>
       </c>
       <c r="Y5" t="n">
-        <v>189.7417362190987</v>
+        <v>191.5585926512467</v>
       </c>
     </row>
     <row r="6">
@@ -4613,25 +4613,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>394.6673863086054</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="C6" t="n">
-        <v>29.92</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="D6" t="n">
-        <v>29.92</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="E6" t="n">
-        <v>29.92</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="F6" t="n">
-        <v>29.92</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="G6" t="n">
-        <v>29.92</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="H6" t="n">
-        <v>29.92</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="I6" t="n">
         <v>29.92</v>
@@ -4661,28 +4661,28 @@
         <v>1346.247111942856</v>
       </c>
       <c r="R6" t="n">
-        <v>1211.245105910912</v>
+        <v>1112.358993892805</v>
       </c>
       <c r="S6" t="n">
-        <v>1148.125094511552</v>
+        <v>1049.238982493446</v>
       </c>
       <c r="T6" t="n">
-        <v>1143.60646374105</v>
+        <v>1044.720351722944</v>
       </c>
       <c r="U6" t="n">
-        <v>1143.408558894664</v>
+        <v>1044.522446876557</v>
       </c>
       <c r="V6" t="n">
-        <v>1128.75131930727</v>
+        <v>1029.865207289163</v>
       </c>
       <c r="W6" t="n">
-        <v>1096.051174953908</v>
+        <v>997.165062935801</v>
       </c>
       <c r="X6" t="n">
-        <v>1075.987801776748</v>
+        <v>619.3872851580231</v>
       </c>
       <c r="Y6" t="n">
-        <v>698.2100239989707</v>
+        <v>619.3872851580231</v>
       </c>
     </row>
     <row r="7">
@@ -4692,31 +4692,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>253.0866383453244</v>
+        <v>1250.668263144111</v>
       </c>
       <c r="C7" t="n">
-        <v>379.0886441637601</v>
+        <v>1376.670268962547</v>
       </c>
       <c r="D7" t="n">
-        <v>492.4077882887602</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="E7" t="n">
-        <v>610.2366925001733</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="F7" t="n">
-        <v>734.5976650921087</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="G7" t="n">
-        <v>888.1863260609612</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="H7" t="n">
-        <v>1059.321902040031</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="I7" t="n">
-        <v>1285.930876713819</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="J7" t="n">
-        <v>1285.930876713819</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="K7" t="n">
         <v>1386.743548464727</v>
@@ -4743,25 +4743,25 @@
         <v>29.92</v>
       </c>
       <c r="S7" t="n">
-        <v>29.92</v>
+        <v>70.34367574991084</v>
       </c>
       <c r="T7" t="n">
-        <v>29.92</v>
+        <v>259.1973975316665</v>
       </c>
       <c r="U7" t="n">
-        <v>29.92</v>
+        <v>505.7585226289696</v>
       </c>
       <c r="V7" t="n">
-        <v>29.92</v>
+        <v>704.5799155149155</v>
       </c>
       <c r="W7" t="n">
-        <v>29.92</v>
+        <v>876.4708337745928</v>
       </c>
       <c r="X7" t="n">
-        <v>29.92</v>
+        <v>1027.501624798786</v>
       </c>
       <c r="Y7" t="n">
-        <v>141.3293006790323</v>
+        <v>1138.910925477819</v>
       </c>
     </row>
     <row r="8">
@@ -4795,31 +4795,31 @@
         <v>29.92</v>
       </c>
       <c r="J8" t="n">
-        <v>29.92</v>
+        <v>400.18</v>
       </c>
       <c r="K8" t="n">
-        <v>400.18</v>
+        <v>451.8183303517587</v>
       </c>
       <c r="L8" t="n">
-        <v>770.4399999999999</v>
+        <v>697.388108133742</v>
       </c>
       <c r="M8" t="n">
-        <v>1140.7</v>
+        <v>697.388108133742</v>
       </c>
       <c r="N8" t="n">
-        <v>1140.7</v>
+        <v>697.388108133742</v>
       </c>
       <c r="O8" t="n">
-        <v>1140.7</v>
+        <v>1067.648108133742</v>
       </c>
       <c r="P8" t="n">
-        <v>1198.791891866258</v>
+        <v>1125.74</v>
       </c>
       <c r="Q8" t="n">
         <v>1496</v>
       </c>
       <c r="R8" t="n">
-        <v>1494.183143567852</v>
+        <v>1496</v>
       </c>
       <c r="S8" t="n">
         <v>1407.815317606417</v>
@@ -4850,25 +4850,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>394.6673863086054</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="C9" t="n">
-        <v>29.92</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="D9" t="n">
-        <v>29.92</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="E9" t="n">
-        <v>29.92</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="F9" t="n">
-        <v>29.92</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="G9" t="n">
-        <v>29.92</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="H9" t="n">
-        <v>29.92</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="I9" t="n">
         <v>29.92</v>
@@ -4895,31 +4895,31 @@
         <v>1492.786030368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1420.482252030268</v>
+        <v>1492.786030368536</v>
       </c>
       <c r="R9" t="n">
-        <v>1285.480245998324</v>
+        <v>1115.008252590758</v>
       </c>
       <c r="S9" t="n">
-        <v>1222.360234598965</v>
+        <v>737.23047481298</v>
       </c>
       <c r="T9" t="n">
-        <v>1217.841603828463</v>
+        <v>359.4526970352022</v>
       </c>
       <c r="U9" t="n">
-        <v>1217.643698982076</v>
+        <v>309.0302644981606</v>
       </c>
       <c r="V9" t="n">
-        <v>1202.986459394682</v>
+        <v>294.3730249107666</v>
       </c>
       <c r="W9" t="n">
-        <v>1170.28631504132</v>
+        <v>261.6728805574044</v>
       </c>
       <c r="X9" t="n">
-        <v>1150.222941864161</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="Y9" t="n">
-        <v>772.4451640863832</v>
+        <v>241.6095073802453</v>
       </c>
     </row>
     <row r="10">
@@ -4929,31 +4929,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>851.9261246306048</v>
+        <v>663.0724028488492</v>
       </c>
       <c r="C10" t="n">
-        <v>884.9629768229406</v>
+        <v>789.074408667285</v>
       </c>
       <c r="D10" t="n">
-        <v>884.9629768229406</v>
+        <v>789.074408667285</v>
       </c>
       <c r="E10" t="n">
-        <v>884.9629768229406</v>
+        <v>906.903312878698</v>
       </c>
       <c r="F10" t="n">
-        <v>884.9629768229406</v>
+        <v>1031.264285470633</v>
       </c>
       <c r="G10" t="n">
-        <v>884.9629768229406</v>
+        <v>1031.264285470633</v>
       </c>
       <c r="H10" t="n">
-        <v>884.9629768229406</v>
+        <v>1031.264285470633</v>
       </c>
       <c r="I10" t="n">
-        <v>884.9629768229406</v>
+        <v>1031.264285470633</v>
       </c>
       <c r="J10" t="n">
-        <v>1255.222976822941</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="K10" t="n">
         <v>1386.743548464727</v>
@@ -4983,22 +4983,22 @@
         <v>29.92</v>
       </c>
       <c r="T10" t="n">
-        <v>218.7737217817557</v>
+        <v>29.92</v>
       </c>
       <c r="U10" t="n">
-        <v>218.7737217817557</v>
+        <v>29.92</v>
       </c>
       <c r="V10" t="n">
-        <v>417.5951146677016</v>
+        <v>228.741392885946</v>
       </c>
       <c r="W10" t="n">
-        <v>589.486032927379</v>
+        <v>400.6323111456234</v>
       </c>
       <c r="X10" t="n">
-        <v>740.5168239515725</v>
+        <v>551.6631021698169</v>
       </c>
       <c r="Y10" t="n">
-        <v>851.9261246306048</v>
+        <v>663.0724028488492</v>
       </c>
     </row>
     <row r="11">
@@ -5008,22 +5008,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>608.2066695820786</v>
+        <v>607.5035534240029</v>
       </c>
       <c r="C11" t="n">
-        <v>476.4141663063272</v>
+        <v>475.7110501482515</v>
       </c>
       <c r="D11" t="n">
-        <v>384.1523928317314</v>
+        <v>383.4492766736557</v>
       </c>
       <c r="E11" t="n">
-        <v>297.9268477742883</v>
+        <v>297.2237316162127</v>
       </c>
       <c r="F11" t="n">
-        <v>211.1696470591248</v>
+        <v>210.4665309010492</v>
       </c>
       <c r="G11" t="n">
-        <v>127.0464193797368</v>
+        <v>126.3433032216612</v>
       </c>
       <c r="H11" t="n">
         <v>52.4</v>
@@ -5032,16 +5032,16 @@
         <v>52.4</v>
       </c>
       <c r="J11" t="n">
-        <v>567.6776741934345</v>
+        <v>141.6759849731395</v>
       </c>
       <c r="K11" t="n">
-        <v>1216.127674193434</v>
+        <v>790.1259849731395</v>
       </c>
       <c r="L11" t="n">
+        <v>1438.575984973139</v>
+      </c>
+      <c r="M11" t="n">
         <v>1585.241587554807</v>
-      </c>
-      <c r="M11" t="n">
-        <v>2233.691587554807</v>
       </c>
       <c r="N11" t="n">
         <v>2233.691587554807</v>
@@ -5087,22 +5087,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1050.160134179741</v>
+        <v>180.5214748259267</v>
       </c>
       <c r="C12" t="n">
-        <v>1007.634970093358</v>
+        <v>137.9963107395436</v>
       </c>
       <c r="D12" t="n">
-        <v>656.182761105779</v>
+        <v>108.7663239741874</v>
       </c>
       <c r="E12" t="n">
-        <v>632.2715517907158</v>
+        <v>84.85511465912413</v>
       </c>
       <c r="F12" t="n">
-        <v>289.2046403383148</v>
+        <v>64.01042542894548</v>
       </c>
       <c r="G12" t="n">
-        <v>58.00018335964016</v>
+        <v>58.00018335964018</v>
       </c>
       <c r="H12" t="n">
         <v>52.4</v>
@@ -5132,31 +5132,31 @@
         <v>2313.990605368536</v>
       </c>
       <c r="Q12" t="n">
-        <v>2313.990605368536</v>
+        <v>2240.946636437805</v>
       </c>
       <c r="R12" t="n">
-        <v>2132.917892265885</v>
+        <v>1737.651701112932</v>
       </c>
       <c r="S12" t="n">
-        <v>1998.674143492788</v>
+        <v>1451.257706361196</v>
       </c>
       <c r="T12" t="n">
-        <v>1914.658037974811</v>
+        <v>1045.019378620997</v>
       </c>
       <c r="U12" t="n">
-        <v>1832.679830098122</v>
+        <v>963.0411707443078</v>
       </c>
       <c r="V12" t="n">
-        <v>1736.204408692546</v>
+        <v>866.5657493387318</v>
       </c>
       <c r="W12" t="n">
-        <v>1299.46386029878</v>
+        <v>752.0474231671878</v>
       </c>
       <c r="X12" t="n">
-        <v>1197.582305303438</v>
+        <v>327.9436459496247</v>
       </c>
       <c r="Y12" t="n">
-        <v>1116.378878266939</v>
+        <v>246.7402189131253</v>
       </c>
     </row>
     <row r="13">
@@ -5166,31 +5166,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>673.4417775581345</v>
+        <v>673.4417775581344</v>
       </c>
       <c r="C13" t="n">
-        <v>719.2537833765703</v>
+        <v>719.2537833765701</v>
       </c>
       <c r="D13" t="n">
-        <v>752.3829275015703</v>
+        <v>752.3829275015702</v>
       </c>
       <c r="E13" t="n">
-        <v>790.0218317129833</v>
+        <v>790.0218317129832</v>
       </c>
       <c r="F13" t="n">
-        <v>834.1928043049188</v>
+        <v>834.1928043049187</v>
       </c>
       <c r="G13" t="n">
-        <v>908.0645554377057</v>
+        <v>908.0645554377056</v>
       </c>
       <c r="H13" t="n">
         <v>1003.21633305612</v>
       </c>
       <c r="I13" t="n">
-        <v>1163.862419205318</v>
+        <v>1163.862419205317</v>
       </c>
       <c r="J13" t="n">
-        <v>1491.077756743015</v>
+        <v>1491.077756743014</v>
       </c>
       <c r="K13" t="n">
         <v>1597.372803794637</v>
@@ -5199,22 +5199,22 @@
         <v>1591.155096928856</v>
       </c>
       <c r="M13" t="n">
-        <v>1492.275360291076</v>
+        <v>1492.275360291075</v>
       </c>
       <c r="N13" t="n">
-        <v>1339.839881046618</v>
+        <v>1342.71903405416</v>
       </c>
       <c r="O13" t="n">
-        <v>1109.635154952564</v>
+        <v>1112.514307960106</v>
       </c>
       <c r="P13" t="n">
-        <v>818.3161660963807</v>
+        <v>821.1953191039224</v>
       </c>
       <c r="Q13" t="n">
-        <v>466.2233328154396</v>
+        <v>466.2233328154397</v>
       </c>
       <c r="R13" t="n">
-        <v>84.56167017509824</v>
+        <v>84.56167017509823</v>
       </c>
       <c r="S13" t="n">
         <v>52.4</v>
@@ -5223,19 +5223,19 @@
         <v>163.0851070276573</v>
       </c>
       <c r="U13" t="n">
-        <v>329.4820370429932</v>
+        <v>329.4820370429931</v>
       </c>
       <c r="V13" t="n">
         <v>448.1134299289391</v>
       </c>
       <c r="W13" t="n">
-        <v>539.8143481886166</v>
+        <v>539.8143481886165</v>
       </c>
       <c r="X13" t="n">
-        <v>610.6551392128101</v>
+        <v>610.65513921281</v>
       </c>
       <c r="Y13" t="n">
-        <v>641.8744398918424</v>
+        <v>641.8744398918423</v>
       </c>
     </row>
     <row r="14">
@@ -5269,25 +5269,25 @@
         <v>52.4</v>
       </c>
       <c r="J14" t="n">
-        <v>141.6759849731395</v>
+        <v>567.6776741934345</v>
       </c>
       <c r="K14" t="n">
-        <v>790.1259849731395</v>
+        <v>988.9116280297779</v>
       </c>
       <c r="L14" t="n">
-        <v>1438.575984973139</v>
+        <v>1637.361628029778</v>
       </c>
       <c r="M14" t="n">
-        <v>1585.241587554807</v>
+        <v>1637.361628029778</v>
       </c>
       <c r="N14" t="n">
-        <v>2233.691587554807</v>
+        <v>1637.361628029778</v>
       </c>
       <c r="O14" t="n">
-        <v>2410.244759641279</v>
+        <v>1813.91480011625</v>
       </c>
       <c r="P14" t="n">
-        <v>2620</v>
+        <v>2023.670040474971</v>
       </c>
       <c r="Q14" t="n">
         <v>2620</v>
@@ -5296,10 +5296,10 @@
         <v>2620</v>
       </c>
       <c r="S14" t="n">
-        <v>2476.335336314592</v>
+        <v>2477.038452472668</v>
       </c>
       <c r="T14" t="n">
-        <v>2212.479660135798</v>
+        <v>2213.182776293874</v>
       </c>
       <c r="U14" t="n">
         <v>1879.745133467756</v>
@@ -5324,10 +5324,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>727.9379119575182</v>
+        <v>180.5214748259267</v>
       </c>
       <c r="C15" t="n">
-        <v>363.1905256489128</v>
+        <v>137.9963107395436</v>
       </c>
       <c r="D15" t="n">
         <v>108.7663239741874</v>
@@ -5339,7 +5339,7 @@
         <v>64.01042542894548</v>
       </c>
       <c r="G15" t="n">
-        <v>58.00018335964016</v>
+        <v>58.00018335964018</v>
       </c>
       <c r="H15" t="n">
         <v>52.4</v>
@@ -5381,19 +5381,19 @@
         <v>1914.658037974811</v>
       </c>
       <c r="U15" t="n">
-        <v>1832.679830098122</v>
+        <v>1607.485615188752</v>
       </c>
       <c r="V15" t="n">
-        <v>1413.982186470323</v>
+        <v>1188.787971560954</v>
       </c>
       <c r="W15" t="n">
-        <v>1299.463860298779</v>
+        <v>752.0474231671878</v>
       </c>
       <c r="X15" t="n">
-        <v>875.3600830812161</v>
+        <v>327.9436459496247</v>
       </c>
       <c r="Y15" t="n">
-        <v>794.1566560447168</v>
+        <v>246.7402189131253</v>
       </c>
     </row>
     <row r="16">
@@ -5403,31 +5403,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>673.4417775581345</v>
+        <v>673.4417775581344</v>
       </c>
       <c r="C16" t="n">
-        <v>719.2537833765703</v>
+        <v>719.2537833765701</v>
       </c>
       <c r="D16" t="n">
-        <v>752.3829275015703</v>
+        <v>752.3829275015702</v>
       </c>
       <c r="E16" t="n">
-        <v>790.0218317129833</v>
+        <v>790.0218317129832</v>
       </c>
       <c r="F16" t="n">
-        <v>834.1928043049188</v>
+        <v>834.1928043049187</v>
       </c>
       <c r="G16" t="n">
-        <v>908.0645554377057</v>
+        <v>908.0645554377056</v>
       </c>
       <c r="H16" t="n">
         <v>1003.21633305612</v>
       </c>
       <c r="I16" t="n">
-        <v>1163.862419205318</v>
+        <v>1163.862419205317</v>
       </c>
       <c r="J16" t="n">
-        <v>1491.077756743015</v>
+        <v>1491.077756743014</v>
       </c>
       <c r="K16" t="n">
         <v>1597.372803794637</v>
@@ -5436,7 +5436,7 @@
         <v>1591.155096928856</v>
       </c>
       <c r="M16" t="n">
-        <v>1492.275360291076</v>
+        <v>1492.275360291075</v>
       </c>
       <c r="N16" t="n">
         <v>1339.839881046618</v>
@@ -5448,10 +5448,10 @@
         <v>818.3161660963807</v>
       </c>
       <c r="Q16" t="n">
-        <v>463.3441798078979</v>
+        <v>466.2233328154397</v>
       </c>
       <c r="R16" t="n">
-        <v>81.68251716755651</v>
+        <v>84.56167017509823</v>
       </c>
       <c r="S16" t="n">
         <v>52.4</v>
@@ -5460,19 +5460,19 @@
         <v>163.0851070276573</v>
       </c>
       <c r="U16" t="n">
-        <v>329.4820370429932</v>
+        <v>329.4820370429931</v>
       </c>
       <c r="V16" t="n">
         <v>448.1134299289391</v>
       </c>
       <c r="W16" t="n">
-        <v>539.8143481886166</v>
+        <v>539.8143481886165</v>
       </c>
       <c r="X16" t="n">
-        <v>610.6551392128101</v>
+        <v>610.65513921281</v>
       </c>
       <c r="Y16" t="n">
-        <v>641.8744398918424</v>
+        <v>641.8744398918423</v>
       </c>
     </row>
     <row r="17">
@@ -5509,22 +5509,22 @@
         <v>141.6759849731395</v>
       </c>
       <c r="K17" t="n">
-        <v>790.1259849731395</v>
+        <v>327.4727226113304</v>
       </c>
       <c r="L17" t="n">
-        <v>1438.575984973139</v>
+        <v>726.7700404749689</v>
       </c>
       <c r="M17" t="n">
-        <v>2087.02598497314</v>
+        <v>726.7700404749689</v>
       </c>
       <c r="N17" t="n">
-        <v>2233.691587554807</v>
+        <v>726.7700404749689</v>
       </c>
       <c r="O17" t="n">
-        <v>2410.244759641279</v>
+        <v>1375.22004047497</v>
       </c>
       <c r="P17" t="n">
-        <v>2620</v>
+        <v>2023.670040474971</v>
       </c>
       <c r="Q17" t="n">
         <v>2620</v>
@@ -5533,19 +5533,19 @@
         <v>2620</v>
       </c>
       <c r="S17" t="n">
-        <v>2476.335336314592</v>
+        <v>2477.038452472668</v>
       </c>
       <c r="T17" t="n">
-        <v>2212.479660135798</v>
+        <v>2213.182776293874</v>
       </c>
       <c r="U17" t="n">
-        <v>1879.04201730968</v>
+        <v>1879.745133467756</v>
       </c>
       <c r="V17" t="n">
-        <v>1565.051083807838</v>
+        <v>1565.754199965913</v>
       </c>
       <c r="W17" t="n">
-        <v>1242.451613120012</v>
+        <v>1243.154729278087</v>
       </c>
       <c r="X17" t="n">
         <v>967.1124732572108</v>
@@ -5621,16 +5621,16 @@
         <v>1832.679830098122</v>
       </c>
       <c r="V18" t="n">
-        <v>1413.982186470323</v>
+        <v>1736.204408692546</v>
       </c>
       <c r="W18" t="n">
-        <v>977.2416380765571</v>
+        <v>1299.46386029878</v>
       </c>
       <c r="X18" t="n">
-        <v>553.1378608589939</v>
+        <v>875.3600830812163</v>
       </c>
       <c r="Y18" t="n">
-        <v>246.7402189131253</v>
+        <v>471.9344338224947</v>
       </c>
     </row>
     <row r="19">
@@ -5719,13 +5719,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>608.2066695820786</v>
+        <v>607.5035534240029</v>
       </c>
       <c r="C20" t="n">
-        <v>476.4141663063272</v>
+        <v>475.7110501482515</v>
       </c>
       <c r="D20" t="n">
-        <v>384.1523928317314</v>
+        <v>383.4492766736557</v>
       </c>
       <c r="E20" t="n">
         <v>297.9268477742883</v>
@@ -5743,22 +5743,22 @@
         <v>52.4</v>
       </c>
       <c r="J20" t="n">
-        <v>567.6776741934345</v>
+        <v>141.6759849731395</v>
       </c>
       <c r="K20" t="n">
-        <v>1216.127674193434</v>
+        <v>327.4727226113304</v>
       </c>
       <c r="L20" t="n">
-        <v>1864.577674193434</v>
+        <v>557.9700049228883</v>
       </c>
       <c r="M20" t="n">
-        <v>2233.691587554807</v>
+        <v>1206.42000492289</v>
       </c>
       <c r="N20" t="n">
-        <v>2233.691587554807</v>
+        <v>1323.099999999996</v>
       </c>
       <c r="O20" t="n">
-        <v>2410.244759641279</v>
+        <v>1971.549999999998</v>
       </c>
       <c r="P20" t="n">
         <v>2620</v>
@@ -5770,25 +5770,25 @@
         <v>2620</v>
       </c>
       <c r="S20" t="n">
-        <v>2477.038452472668</v>
+        <v>2476.335336314592</v>
       </c>
       <c r="T20" t="n">
-        <v>2213.182776293874</v>
+        <v>2212.479660135798</v>
       </c>
       <c r="U20" t="n">
-        <v>1879.745133467756</v>
+        <v>1879.04201730968</v>
       </c>
       <c r="V20" t="n">
-        <v>1565.754199965913</v>
+        <v>1565.051083807838</v>
       </c>
       <c r="W20" t="n">
-        <v>1243.154729278087</v>
+        <v>1242.451613120012</v>
       </c>
       <c r="X20" t="n">
-        <v>967.1124732572108</v>
+        <v>966.4093570991351</v>
       </c>
       <c r="Y20" t="n">
-        <v>772.852440244275</v>
+        <v>772.1493240861994</v>
       </c>
     </row>
     <row r="21">
@@ -5798,22 +5798,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1147.188141492594</v>
+        <v>1372.382356401963</v>
       </c>
       <c r="C21" t="n">
-        <v>782.4407551839881</v>
+        <v>1329.85719231558</v>
       </c>
       <c r="D21" t="n">
-        <v>430.9885461964096</v>
+        <v>978.4049833280014</v>
       </c>
       <c r="E21" t="n">
-        <v>84.85511465912413</v>
+        <v>632.2715517907159</v>
       </c>
       <c r="F21" t="n">
-        <v>64.01042542894548</v>
+        <v>289.204640338315</v>
       </c>
       <c r="G21" t="n">
-        <v>58.00018335964016</v>
+        <v>283.1943982690096</v>
       </c>
       <c r="H21" t="n">
         <v>52.4</v>
@@ -5956,19 +5956,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>608.2066695820786</v>
+        <v>607.5035534240029</v>
       </c>
       <c r="C23" t="n">
-        <v>476.4141663063272</v>
+        <v>475.7110501482515</v>
       </c>
       <c r="D23" t="n">
-        <v>384.1523928317314</v>
+        <v>383.4492766736557</v>
       </c>
       <c r="E23" t="n">
-        <v>297.9268477742883</v>
+        <v>297.2237316162127</v>
       </c>
       <c r="F23" t="n">
-        <v>211.1696470591248</v>
+        <v>210.4665309010492</v>
       </c>
       <c r="G23" t="n">
         <v>127.0464193797368</v>
@@ -5980,16 +5980,16 @@
         <v>52.4</v>
       </c>
       <c r="J23" t="n">
-        <v>567.6776741934345</v>
+        <v>141.6759849731395</v>
       </c>
       <c r="K23" t="n">
-        <v>1216.127674193434</v>
+        <v>790.1259849731395</v>
       </c>
       <c r="L23" t="n">
-        <v>1864.577674193434</v>
+        <v>1438.575984973139</v>
       </c>
       <c r="M23" t="n">
-        <v>2233.691587554807</v>
+        <v>1585.241587554802</v>
       </c>
       <c r="N23" t="n">
         <v>2233.691587554807</v>
@@ -6007,25 +6007,25 @@
         <v>2620</v>
       </c>
       <c r="S23" t="n">
-        <v>2477.038452472668</v>
+        <v>2476.335336314592</v>
       </c>
       <c r="T23" t="n">
-        <v>2213.182776293874</v>
+        <v>2212.479660135798</v>
       </c>
       <c r="U23" t="n">
-        <v>1879.745133467756</v>
+        <v>1879.04201730968</v>
       </c>
       <c r="V23" t="n">
-        <v>1565.754199965913</v>
+        <v>1565.051083807838</v>
       </c>
       <c r="W23" t="n">
-        <v>1243.154729278087</v>
+        <v>1242.451613120012</v>
       </c>
       <c r="X23" t="n">
-        <v>967.1124732572108</v>
+        <v>966.4093570991351</v>
       </c>
       <c r="Y23" t="n">
-        <v>772.852440244275</v>
+        <v>772.1493240861994</v>
       </c>
     </row>
     <row r="24">
@@ -6038,13 +6038,13 @@
         <v>1372.382356401963</v>
       </c>
       <c r="C24" t="n">
-        <v>1007.634970093357</v>
+        <v>1104.66297740621</v>
       </c>
       <c r="D24" t="n">
-        <v>656.182761105779</v>
+        <v>753.2107684186319</v>
       </c>
       <c r="E24" t="n">
-        <v>310.0493295684935</v>
+        <v>407.0773368813464</v>
       </c>
       <c r="F24" t="n">
         <v>64.01042542894548</v>
@@ -6220,13 +6220,13 @@
         <v>567.6776741934345</v>
       </c>
       <c r="K26" t="n">
-        <v>988.9116280297779</v>
+        <v>753.4744118316256</v>
       </c>
       <c r="L26" t="n">
-        <v>1637.361628029778</v>
+        <v>988.9116280297652</v>
       </c>
       <c r="M26" t="n">
-        <v>1637.361628029778</v>
+        <v>988.9116280297652</v>
       </c>
       <c r="N26" t="n">
         <v>1637.361628029778</v>
@@ -6272,22 +6272,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1050.16013417974</v>
+        <v>405.7156897352958</v>
       </c>
       <c r="C27" t="n">
-        <v>1007.634970093357</v>
+        <v>363.1905256489127</v>
       </c>
       <c r="D27" t="n">
-        <v>978.4049833280011</v>
+        <v>333.9605388835565</v>
       </c>
       <c r="E27" t="n">
-        <v>632.2715517907156</v>
+        <v>310.0493295684932</v>
       </c>
       <c r="F27" t="n">
-        <v>289.2046403383147</v>
+        <v>289.2046403383146</v>
       </c>
       <c r="G27" t="n">
-        <v>58.00018335964016</v>
+        <v>283.1943982690092</v>
       </c>
       <c r="H27" t="n">
         <v>52.4</v>
@@ -6323,25 +6323,25 @@
         <v>2132.917892265885</v>
       </c>
       <c r="S27" t="n">
-        <v>1998.674143492788</v>
+        <v>1676.451921270565</v>
       </c>
       <c r="T27" t="n">
-        <v>1914.658037974811</v>
+        <v>1592.435815752589</v>
       </c>
       <c r="U27" t="n">
-        <v>1832.679830098122</v>
+        <v>1510.457607875899</v>
       </c>
       <c r="V27" t="n">
-        <v>1736.204408692546</v>
+        <v>1091.759964248101</v>
       </c>
       <c r="W27" t="n">
-        <v>1621.686082521002</v>
+        <v>655.0194158543347</v>
       </c>
       <c r="X27" t="n">
-        <v>1519.804527525661</v>
+        <v>553.1378608589938</v>
       </c>
       <c r="Y27" t="n">
-        <v>1116.378878266939</v>
+        <v>471.9344338224944</v>
       </c>
     </row>
     <row r="28">
@@ -6351,31 +6351,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>673.4417775581345</v>
+        <v>673.4417775581344</v>
       </c>
       <c r="C28" t="n">
-        <v>719.2537833765703</v>
+        <v>719.2537833765701</v>
       </c>
       <c r="D28" t="n">
-        <v>752.3829275015703</v>
+        <v>752.3829275015702</v>
       </c>
       <c r="E28" t="n">
-        <v>790.0218317129833</v>
+        <v>790.0218317129832</v>
       </c>
       <c r="F28" t="n">
-        <v>834.1928043049188</v>
+        <v>834.1928043049187</v>
       </c>
       <c r="G28" t="n">
-        <v>908.0645554377057</v>
+        <v>908.0645554377056</v>
       </c>
       <c r="H28" t="n">
         <v>1003.21633305612</v>
       </c>
       <c r="I28" t="n">
-        <v>1163.862419205318</v>
+        <v>1163.862419205317</v>
       </c>
       <c r="J28" t="n">
-        <v>1491.077756743015</v>
+        <v>1491.077756743014</v>
       </c>
       <c r="K28" t="n">
         <v>1597.372803794637</v>
@@ -6384,7 +6384,7 @@
         <v>1591.155096928856</v>
       </c>
       <c r="M28" t="n">
-        <v>1492.275360291076</v>
+        <v>1492.275360291075</v>
       </c>
       <c r="N28" t="n">
         <v>1339.839881046618</v>
@@ -6396,10 +6396,10 @@
         <v>818.3161660963807</v>
       </c>
       <c r="Q28" t="n">
-        <v>466.2233328154396</v>
+        <v>463.3441798078979</v>
       </c>
       <c r="R28" t="n">
-        <v>84.56167017509824</v>
+        <v>81.68251716755645</v>
       </c>
       <c r="S28" t="n">
         <v>52.4</v>
@@ -6408,19 +6408,19 @@
         <v>163.0851070276573</v>
       </c>
       <c r="U28" t="n">
-        <v>329.4820370429932</v>
+        <v>329.4820370429931</v>
       </c>
       <c r="V28" t="n">
         <v>448.1134299289391</v>
       </c>
       <c r="W28" t="n">
-        <v>539.8143481886166</v>
+        <v>539.8143481886165</v>
       </c>
       <c r="X28" t="n">
-        <v>610.6551392128101</v>
+        <v>610.65513921281</v>
       </c>
       <c r="Y28" t="n">
-        <v>641.8744398918424</v>
+        <v>641.8744398918423</v>
       </c>
     </row>
     <row r="29">
@@ -6430,19 +6430,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>607.5035534240029</v>
+        <v>608.2066695820786</v>
       </c>
       <c r="C29" t="n">
-        <v>475.7110501482515</v>
+        <v>476.4141663063272</v>
       </c>
       <c r="D29" t="n">
-        <v>383.4492766736557</v>
+        <v>384.1523928317314</v>
       </c>
       <c r="E29" t="n">
-        <v>297.2237316162127</v>
+        <v>297.9268477742883</v>
       </c>
       <c r="F29" t="n">
-        <v>210.4665309010492</v>
+        <v>211.1696470591248</v>
       </c>
       <c r="G29" t="n">
         <v>127.0464193797368</v>
@@ -6457,10 +6457,10 @@
         <v>567.6776741934345</v>
       </c>
       <c r="K29" t="n">
-        <v>753.4744118316256</v>
+        <v>1216.127674193434</v>
       </c>
       <c r="L29" t="n">
-        <v>988.9116280297577</v>
+        <v>1637.361628029778</v>
       </c>
       <c r="M29" t="n">
         <v>1637.361628029778</v>
@@ -6487,19 +6487,19 @@
         <v>2212.479660135798</v>
       </c>
       <c r="U29" t="n">
-        <v>1879.04201730968</v>
+        <v>1879.745133467756</v>
       </c>
       <c r="V29" t="n">
-        <v>1565.051083807838</v>
+        <v>1565.754199965913</v>
       </c>
       <c r="W29" t="n">
-        <v>1242.451613120012</v>
+        <v>1243.154729278087</v>
       </c>
       <c r="X29" t="n">
-        <v>966.4093570991351</v>
+        <v>967.1124732572108</v>
       </c>
       <c r="Y29" t="n">
-        <v>772.1493240861994</v>
+        <v>772.852440244275</v>
       </c>
     </row>
     <row r="30">
@@ -6509,25 +6509,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>824.9659192703713</v>
+        <v>1339.054416549606</v>
       </c>
       <c r="C30" t="n">
-        <v>782.4407551839881</v>
+        <v>1296.529252463223</v>
       </c>
       <c r="D30" t="n">
-        <v>753.2107684186319</v>
+        <v>945.077043475645</v>
       </c>
       <c r="E30" t="n">
-        <v>407.0773368813464</v>
+        <v>598.9436119383595</v>
       </c>
       <c r="F30" t="n">
-        <v>64.01042542894548</v>
+        <v>255.8767004859585</v>
       </c>
       <c r="G30" t="n">
-        <v>58.00018335964018</v>
+        <v>249.8664584166532</v>
       </c>
       <c r="H30" t="n">
-        <v>52.4</v>
+        <v>244.266275057013</v>
       </c>
       <c r="I30" t="n">
         <v>52.4</v>
@@ -6569,16 +6569,16 @@
         <v>1832.679830098122</v>
       </c>
       <c r="V30" t="n">
-        <v>1511.010193783176</v>
+        <v>1736.204408692546</v>
       </c>
       <c r="W30" t="n">
-        <v>1396.491867611632</v>
+        <v>1621.686082521002</v>
       </c>
       <c r="X30" t="n">
-        <v>972.3880903940692</v>
+        <v>1519.804527525661</v>
       </c>
       <c r="Y30" t="n">
-        <v>891.1846633575699</v>
+        <v>1405.273160636805</v>
       </c>
     </row>
     <row r="31">
@@ -6588,55 +6588,55 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>673.4417775581344</v>
+        <v>673.4417775581345</v>
       </c>
       <c r="C31" t="n">
-        <v>719.2537833765701</v>
+        <v>719.2537833765703</v>
       </c>
       <c r="D31" t="n">
-        <v>752.3829275015702</v>
+        <v>752.3829275015703</v>
       </c>
       <c r="E31" t="n">
-        <v>790.0218317129832</v>
+        <v>790.0218317129833</v>
       </c>
       <c r="F31" t="n">
-        <v>834.1928043049187</v>
+        <v>834.1928043049188</v>
       </c>
       <c r="G31" t="n">
-        <v>908.0645554377056</v>
+        <v>908.0645554377057</v>
       </c>
       <c r="H31" t="n">
         <v>1003.21633305612</v>
       </c>
       <c r="I31" t="n">
-        <v>1163.862419205317</v>
+        <v>1163.862419205318</v>
       </c>
       <c r="J31" t="n">
-        <v>1491.077756743014</v>
+        <v>1491.077756743015</v>
       </c>
       <c r="K31" t="n">
         <v>1597.372803794637</v>
       </c>
       <c r="L31" t="n">
-        <v>1594.034249936398</v>
+        <v>1591.155096928856</v>
       </c>
       <c r="M31" t="n">
-        <v>1495.154513298618</v>
+        <v>1492.275360291076</v>
       </c>
       <c r="N31" t="n">
-        <v>1342.71903405416</v>
+        <v>1339.839881046618</v>
       </c>
       <c r="O31" t="n">
-        <v>1112.514307960106</v>
+        <v>1109.635154952564</v>
       </c>
       <c r="P31" t="n">
-        <v>821.1953191039224</v>
+        <v>818.3161660963807</v>
       </c>
       <c r="Q31" t="n">
-        <v>466.2233328154397</v>
+        <v>463.3441798078979</v>
       </c>
       <c r="R31" t="n">
-        <v>84.56167017509823</v>
+        <v>81.68251716755651</v>
       </c>
       <c r="S31" t="n">
         <v>52.4</v>
@@ -6645,19 +6645,19 @@
         <v>163.0851070276573</v>
       </c>
       <c r="U31" t="n">
-        <v>329.4820370429931</v>
+        <v>329.4820370429932</v>
       </c>
       <c r="V31" t="n">
         <v>448.1134299289391</v>
       </c>
       <c r="W31" t="n">
-        <v>539.8143481886165</v>
+        <v>539.8143481886166</v>
       </c>
       <c r="X31" t="n">
-        <v>610.65513921281</v>
+        <v>610.6551392128101</v>
       </c>
       <c r="Y31" t="n">
-        <v>641.8744398918423</v>
+        <v>641.8744398918424</v>
       </c>
     </row>
     <row r="32">
@@ -6691,16 +6691,16 @@
         <v>52.4</v>
       </c>
       <c r="J32" t="n">
-        <v>567.6776741934345</v>
+        <v>141.6759849731395</v>
       </c>
       <c r="K32" t="n">
-        <v>1216.127674193434</v>
+        <v>790.1259849731395</v>
       </c>
       <c r="L32" t="n">
-        <v>1585.241587554774</v>
+        <v>1438.575984973139</v>
       </c>
       <c r="M32" t="n">
-        <v>2233.691587554807</v>
+        <v>2087.025984973172</v>
       </c>
       <c r="N32" t="n">
         <v>2233.691587554807</v>
@@ -6791,28 +6791,28 @@
         <v>2313.990605368536</v>
       </c>
       <c r="Q33" t="n">
-        <v>2313.990605368536</v>
+        <v>2240.946636437805</v>
       </c>
       <c r="R33" t="n">
-        <v>2132.917892265885</v>
+        <v>1737.651701112932</v>
       </c>
       <c r="S33" t="n">
-        <v>1998.674143492788</v>
+        <v>1281.185730117613</v>
       </c>
       <c r="T33" t="n">
-        <v>1914.658037974811</v>
+        <v>1045.019378620997</v>
       </c>
       <c r="U33" t="n">
-        <v>1832.679830098122</v>
+        <v>963.0411707443078</v>
       </c>
       <c r="V33" t="n">
-        <v>1413.982186470323</v>
+        <v>866.5657493387318</v>
       </c>
       <c r="W33" t="n">
-        <v>977.2416380765571</v>
+        <v>752.0474231671878</v>
       </c>
       <c r="X33" t="n">
-        <v>553.1378608589939</v>
+        <v>650.1658681718469</v>
       </c>
       <c r="Y33" t="n">
         <v>246.7402189131253</v>
@@ -6825,55 +6825,55 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>673.4417775581446</v>
+        <v>673.4417775581344</v>
       </c>
       <c r="C34" t="n">
-        <v>719.2537833765804</v>
+        <v>719.2537833765783</v>
       </c>
       <c r="D34" t="n">
-        <v>752.3829275015804</v>
+        <v>752.3829275015784</v>
       </c>
       <c r="E34" t="n">
-        <v>790.0218317129934</v>
+        <v>790.0218317129913</v>
       </c>
       <c r="F34" t="n">
-        <v>834.1928043049289</v>
+        <v>834.1928043049269</v>
       </c>
       <c r="G34" t="n">
-        <v>908.0645554377159</v>
+        <v>908.0645554377138</v>
       </c>
       <c r="H34" t="n">
-        <v>1003.21633305613</v>
+        <v>1003.216333056128</v>
       </c>
       <c r="I34" t="n">
-        <v>1163.862419205328</v>
+        <v>1163.862419205325</v>
       </c>
       <c r="J34" t="n">
-        <v>1491.077756743025</v>
+        <v>1491.077756743023</v>
       </c>
       <c r="K34" t="n">
-        <v>1597.372803794647</v>
+        <v>1597.372803794645</v>
       </c>
       <c r="L34" t="n">
-        <v>1591.155096928866</v>
+        <v>1591.155096928864</v>
       </c>
       <c r="M34" t="n">
-        <v>1492.275360291086</v>
+        <v>1492.275360291084</v>
       </c>
       <c r="N34" t="n">
-        <v>1339.839881046629</v>
+        <v>1339.839881046626</v>
       </c>
       <c r="O34" t="n">
-        <v>1109.635154952575</v>
+        <v>1109.635154952573</v>
       </c>
       <c r="P34" t="n">
-        <v>818.3161660963912</v>
+        <v>818.3161660963889</v>
       </c>
       <c r="Q34" t="n">
-        <v>463.3441798079083</v>
+        <v>463.3441798079061</v>
       </c>
       <c r="R34" t="n">
-        <v>81.68251716756691</v>
+        <v>81.68251716756464</v>
       </c>
       <c r="S34" t="n">
         <v>52.4</v>
@@ -6904,19 +6904,19 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>113.806583727033</v>
+        <v>117.1408562629478</v>
       </c>
       <c r="C35" t="n">
-        <v>60.80195923916038</v>
+        <v>64.13623177507515</v>
       </c>
       <c r="D35" t="n">
-        <v>47.32806455244342</v>
+        <v>50.66233708835819</v>
       </c>
       <c r="E35" t="n">
-        <v>39.89039828287913</v>
+        <v>43.2246708187939</v>
       </c>
       <c r="F35" t="n">
-        <v>31.92107635559443</v>
+        <v>35.25534889150919</v>
       </c>
       <c r="G35" t="n">
         <v>29.92</v>
@@ -6928,25 +6928,25 @@
         <v>29.92</v>
       </c>
       <c r="J35" t="n">
-        <v>119.1959849731395</v>
+        <v>400.1800000000577</v>
       </c>
       <c r="K35" t="n">
-        <v>369.1715875547493</v>
+        <v>585.9767376382487</v>
       </c>
       <c r="L35" t="n">
-        <v>739.4315875547493</v>
+        <v>816.4740199498065</v>
       </c>
       <c r="M35" t="n">
-        <v>1109.691587554807</v>
+        <v>816.4740199498065</v>
       </c>
       <c r="N35" t="n">
-        <v>1109.691587554807</v>
+        <v>816.4740199498065</v>
       </c>
       <c r="O35" t="n">
-        <v>1286.24475964128</v>
+        <v>993.0271920362791</v>
       </c>
       <c r="P35" t="n">
-        <v>1496</v>
+        <v>1202.782432394999</v>
       </c>
       <c r="Q35" t="n">
         <v>1496</v>
@@ -6973,7 +6973,7 @@
         <v>315.1366298264077</v>
       </c>
       <c r="Y35" t="n">
-        <v>199.6644756013507</v>
+        <v>202.9987481372655</v>
       </c>
     </row>
     <row r="36">
@@ -6983,22 +6983,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>746.1195952961839</v>
+        <v>143.0894165462285</v>
       </c>
       <c r="C36" t="n">
-        <v>381.3722089875785</v>
+        <v>143.0894165462285</v>
       </c>
       <c r="D36" t="n">
-        <v>29.92</v>
+        <v>143.0894165462285</v>
       </c>
       <c r="E36" t="n">
-        <v>29.92</v>
+        <v>143.0894165462285</v>
       </c>
       <c r="F36" t="n">
-        <v>29.92</v>
+        <v>143.0894165462285</v>
       </c>
       <c r="G36" t="n">
-        <v>29.92</v>
+        <v>143.0894165462285</v>
       </c>
       <c r="H36" t="n">
         <v>29.92</v>
@@ -7013,16 +7013,16 @@
         <v>543.0996394772296</v>
       </c>
       <c r="L36" t="n">
-        <v>599.927050901758</v>
+        <v>913.3596394772874</v>
       </c>
       <c r="M36" t="n">
-        <v>884.0224426446173</v>
+        <v>913.3596394772874</v>
       </c>
       <c r="N36" t="n">
-        <v>884.0224426446173</v>
+        <v>1249.89563795278</v>
       </c>
       <c r="O36" t="n">
-        <v>1234.237999492757</v>
+        <v>1296.022377785868</v>
       </c>
       <c r="P36" t="n">
         <v>1496</v>
@@ -7049,10 +7049,10 @@
         <v>1276.422749879739</v>
       </c>
       <c r="X36" t="n">
-        <v>1253.329073672277</v>
+        <v>898.6449721019019</v>
       </c>
       <c r="Y36" t="n">
-        <v>1123.897373073962</v>
+        <v>520.8671943240652</v>
       </c>
     </row>
     <row r="37">
@@ -7062,34 +7062,34 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>247.1466383453244</v>
+        <v>807.7452776445313</v>
       </c>
       <c r="C37" t="n">
-        <v>370.1786441637602</v>
+        <v>807.7452776445313</v>
       </c>
       <c r="D37" t="n">
-        <v>480.5277882887602</v>
+        <v>807.7452776445313</v>
       </c>
       <c r="E37" t="n">
-        <v>548.2813936935061</v>
+        <v>807.7452776445313</v>
       </c>
       <c r="F37" t="n">
-        <v>548.2813936935061</v>
+        <v>929.1362502364667</v>
       </c>
       <c r="G37" t="n">
-        <v>699.3731448262929</v>
+        <v>929.1362502364667</v>
       </c>
       <c r="H37" t="n">
-        <v>871.7449224447068</v>
+        <v>984.1339439954814</v>
       </c>
       <c r="I37" t="n">
-        <v>871.7449224447068</v>
+        <v>984.1339439954814</v>
       </c>
       <c r="J37" t="n">
-        <v>883.150259982404</v>
+        <v>995.5392815331786</v>
       </c>
       <c r="K37" t="n">
-        <v>1066.665307034026</v>
+        <v>995.5392815331786</v>
       </c>
       <c r="L37" t="n">
         <v>1066.665307034026</v>
@@ -7119,19 +7119,19 @@
         <v>29.92</v>
       </c>
       <c r="U37" t="n">
-        <v>29.92</v>
+        <v>273.5369300153358</v>
       </c>
       <c r="V37" t="n">
-        <v>29.92</v>
+        <v>273.5369300153358</v>
       </c>
       <c r="W37" t="n">
-        <v>29.92</v>
+        <v>442.4578482750132</v>
       </c>
       <c r="X37" t="n">
-        <v>29.92</v>
+        <v>590.5186392992068</v>
       </c>
       <c r="Y37" t="n">
-        <v>138.3593006790323</v>
+        <v>698.9579399782391</v>
       </c>
     </row>
     <row r="38">
@@ -7141,16 +7141,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>117.1408562629478</v>
+        <v>113.806583727033</v>
       </c>
       <c r="C38" t="n">
-        <v>64.13623177507512</v>
+        <v>60.80195923916038</v>
       </c>
       <c r="D38" t="n">
-        <v>50.66233708835816</v>
+        <v>47.32806455244342</v>
       </c>
       <c r="E38" t="n">
-        <v>43.22467081879388</v>
+        <v>39.89039828287913</v>
       </c>
       <c r="F38" t="n">
         <v>35.25534889150917</v>
@@ -7192,25 +7192,25 @@
         <v>1496</v>
       </c>
       <c r="S38" t="n">
-        <v>1434.457487638385</v>
+        <v>1431.123215102471</v>
       </c>
       <c r="T38" t="n">
-        <v>1249.38969024747</v>
+        <v>1246.055417711555</v>
       </c>
       <c r="U38" t="n">
-        <v>994.7399262092307</v>
+        <v>991.4056536733159</v>
       </c>
       <c r="V38" t="n">
-        <v>759.5368714952672</v>
+        <v>756.2025989593524</v>
       </c>
       <c r="W38" t="n">
-        <v>515.7252795953201</v>
+        <v>512.3910070594054</v>
       </c>
       <c r="X38" t="n">
-        <v>318.4709023623224</v>
+        <v>315.1366298264077</v>
       </c>
       <c r="Y38" t="n">
-        <v>202.9987481372655</v>
+        <v>199.6644756013507</v>
       </c>
     </row>
     <row r="39">
@@ -7220,76 +7220,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>221.786275057013</v>
+        <v>1250.913525423656</v>
       </c>
       <c r="C39" t="n">
-        <v>221.786275057013</v>
+        <v>1070.572551977265</v>
       </c>
       <c r="D39" t="n">
-        <v>221.786275057013</v>
+        <v>719.1203429896864</v>
       </c>
       <c r="E39" t="n">
-        <v>221.786275057013</v>
+        <v>372.9869114524009</v>
       </c>
       <c r="F39" t="n">
-        <v>221.786275057013</v>
+        <v>29.92</v>
       </c>
       <c r="G39" t="n">
-        <v>221.786275057013</v>
+        <v>29.92</v>
       </c>
       <c r="H39" t="n">
-        <v>221.786275057013</v>
+        <v>29.92</v>
       </c>
       <c r="I39" t="n">
         <v>29.92</v>
       </c>
       <c r="J39" t="n">
-        <v>227.711345930016</v>
+        <v>29.92</v>
       </c>
       <c r="K39" t="n">
-        <v>543.0996394772296</v>
+        <v>345.3082935472136</v>
       </c>
       <c r="L39" t="n">
-        <v>863.9779994927574</v>
+        <v>715.5682935473055</v>
       </c>
       <c r="M39" t="n">
-        <v>863.9779994927574</v>
+        <v>715.5682935473055</v>
       </c>
       <c r="N39" t="n">
-        <v>863.9779994927574</v>
+        <v>1052.104292022798</v>
       </c>
       <c r="O39" t="n">
-        <v>1234.237999492757</v>
+        <v>1422.36429202289</v>
       </c>
       <c r="P39" t="n">
         <v>1496</v>
       </c>
       <c r="Q39" t="n">
-        <v>1422.95603106927</v>
+        <v>1496</v>
       </c>
       <c r="R39" t="n">
-        <v>1099.265599167633</v>
+        <v>1393.715165685228</v>
       </c>
       <c r="S39" t="n">
-        <v>1043.809729182414</v>
+        <v>1338.259295700009</v>
       </c>
       <c r="T39" t="n">
-        <v>1038.581502452317</v>
+        <v>1333.031068969912</v>
       </c>
       <c r="U39" t="n">
-        <v>660.8037246745388</v>
+        <v>1329.840739881101</v>
       </c>
       <c r="V39" t="n">
-        <v>283.025946896761</v>
+        <v>1312.153197263404</v>
       </c>
       <c r="W39" t="n">
-        <v>247.2954995130958</v>
+        <v>1276.422749879739</v>
       </c>
       <c r="X39" t="n">
-        <v>224.2018233056336</v>
+        <v>1253.329073672277</v>
       </c>
       <c r="Y39" t="n">
-        <v>221.786275057013</v>
+        <v>1250.913525423656</v>
       </c>
     </row>
     <row r="40">
@@ -7299,28 +7299,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>225.7713928859459</v>
+        <v>54.42732654938716</v>
       </c>
       <c r="C40" t="n">
-        <v>225.7713928859459</v>
+        <v>54.42732654938716</v>
       </c>
       <c r="D40" t="n">
-        <v>336.120537010946</v>
+        <v>164.7764706743872</v>
       </c>
       <c r="E40" t="n">
-        <v>336.120537010946</v>
+        <v>164.7764706743872</v>
       </c>
       <c r="F40" t="n">
-        <v>336.120537010946</v>
+        <v>286.1674432663227</v>
       </c>
       <c r="G40" t="n">
-        <v>487.2122881437329</v>
+        <v>286.1674432663227</v>
       </c>
       <c r="H40" t="n">
-        <v>659.5840657621469</v>
+        <v>458.5392208847367</v>
       </c>
       <c r="I40" t="n">
-        <v>897.4501519113446</v>
+        <v>696.4053070339344</v>
       </c>
       <c r="J40" t="n">
         <v>1066.665307034026</v>
@@ -7350,25 +7350,25 @@
         <v>29.92</v>
       </c>
       <c r="S40" t="n">
-        <v>29.92</v>
+        <v>54.42732654938716</v>
       </c>
       <c r="T40" t="n">
-        <v>29.92</v>
+        <v>54.42732654938716</v>
       </c>
       <c r="U40" t="n">
-        <v>29.92</v>
+        <v>54.42732654938716</v>
       </c>
       <c r="V40" t="n">
-        <v>225.7713928859459</v>
+        <v>54.42732654938716</v>
       </c>
       <c r="W40" t="n">
-        <v>225.7713928859459</v>
+        <v>54.42732654938716</v>
       </c>
       <c r="X40" t="n">
-        <v>225.7713928859459</v>
+        <v>54.42732654938716</v>
       </c>
       <c r="Y40" t="n">
-        <v>225.7713928859459</v>
+        <v>54.42732654938716</v>
       </c>
     </row>
     <row r="41">
@@ -7378,16 +7378,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>413.4831278362368</v>
+        <v>418.9877005956691</v>
       </c>
       <c r="C41" t="n">
-        <v>255.4279982978591</v>
+        <v>260.9325710572914</v>
       </c>
       <c r="D41" t="n">
-        <v>255.4279982978591</v>
+        <v>142.4081713200694</v>
       </c>
       <c r="E41" t="n">
-        <v>142.9398269777898</v>
+        <v>29.92</v>
       </c>
       <c r="F41" t="n">
         <v>29.92</v>
@@ -7405,16 +7405,16 @@
         <v>400.1800000001369</v>
       </c>
       <c r="K41" t="n">
-        <v>770.4400000001369</v>
+        <v>585.9767376383279</v>
       </c>
       <c r="L41" t="n">
-        <v>1109.691587554807</v>
+        <v>915.9847596411428</v>
       </c>
       <c r="M41" t="n">
-        <v>1109.691587554807</v>
+        <v>915.9847596411428</v>
       </c>
       <c r="N41" t="n">
-        <v>1109.691587554807</v>
+        <v>915.9847596411428</v>
       </c>
       <c r="O41" t="n">
         <v>1286.24475964128</v>
@@ -7429,25 +7429,25 @@
         <v>1496</v>
       </c>
       <c r="S41" t="n">
-        <v>1326.072710051965</v>
+        <v>1496</v>
       </c>
       <c r="T41" t="n">
-        <v>1326.072710051965</v>
+        <v>1496</v>
       </c>
       <c r="U41" t="n">
-        <v>1102.598784551158</v>
+        <v>1136.299730911256</v>
       </c>
       <c r="V41" t="n">
-        <v>762.345224786689</v>
+        <v>796.0461711467871</v>
       </c>
       <c r="W41" t="n">
-        <v>413.4831278362368</v>
+        <v>447.184074196335</v>
       </c>
       <c r="X41" t="n">
-        <v>413.4831278362368</v>
+        <v>447.184074196335</v>
       </c>
       <c r="Y41" t="n">
-        <v>413.4831278362368</v>
+        <v>447.184074196335</v>
       </c>
     </row>
     <row r="42">
@@ -7457,22 +7457,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>315.6172324016843</v>
+        <v>318.0281146697905</v>
       </c>
       <c r="C42" t="n">
-        <v>246.8294420526749</v>
+        <v>249.240324320781</v>
       </c>
       <c r="D42" t="n">
-        <v>191.3368290246924</v>
+        <v>193.7477112927986</v>
       </c>
       <c r="E42" t="n">
-        <v>141.1629934470029</v>
+        <v>143.5738757151091</v>
       </c>
       <c r="F42" t="n">
-        <v>94.05567795419802</v>
+        <v>96.46656022230415</v>
       </c>
       <c r="G42" t="n">
-        <v>61.78280962226643</v>
+        <v>64.19369189037258</v>
       </c>
       <c r="H42" t="n">
         <v>29.92</v>
@@ -7481,52 +7481,52 @@
         <v>29.92</v>
       </c>
       <c r="J42" t="n">
-        <v>227.711345930016</v>
+        <v>29.92</v>
       </c>
       <c r="K42" t="n">
-        <v>543.0996394772296</v>
+        <v>52.38685509283023</v>
       </c>
       <c r="L42" t="n">
-        <v>863.9779994927574</v>
+        <v>422.6468550928302</v>
       </c>
       <c r="M42" t="n">
-        <v>863.9779994927574</v>
+        <v>706.7422468356895</v>
       </c>
       <c r="N42" t="n">
-        <v>863.9779994927574</v>
+        <v>1043.278245311182</v>
       </c>
       <c r="O42" t="n">
-        <v>1234.237999492757</v>
+        <v>1413.538245311182</v>
       </c>
       <c r="P42" t="n">
         <v>1496</v>
       </c>
       <c r="Q42" t="n">
-        <v>1493.589117731894</v>
+        <v>1496</v>
       </c>
       <c r="R42" t="n">
-        <v>1286.253778366616</v>
+        <v>1288.664660634723</v>
       </c>
       <c r="S42" t="n">
-        <v>1125.747403330893</v>
+        <v>1128.158285598999</v>
       </c>
       <c r="T42" t="n">
-        <v>1015.46867155029</v>
+        <v>1017.879553818396</v>
       </c>
       <c r="U42" t="n">
-        <v>907.2278374109744</v>
+        <v>909.6387196790806</v>
       </c>
       <c r="V42" t="n">
-        <v>784.4897897427722</v>
+        <v>786.9006720108785</v>
       </c>
       <c r="W42" t="n">
-        <v>643.708837308602</v>
+        <v>646.1197195767082</v>
       </c>
       <c r="X42" t="n">
-        <v>515.5646560506348</v>
+        <v>517.975538318741</v>
       </c>
       <c r="Y42" t="n">
-        <v>408.0986027515092</v>
+        <v>410.5094850196153</v>
       </c>
     </row>
     <row r="43">
@@ -7566,22 +7566,22 @@
         <v>1163.052803794637</v>
       </c>
       <c r="L43" t="n">
-        <v>1163.052803794637</v>
+        <v>1130.57247066623</v>
       </c>
       <c r="M43" t="n">
-        <v>1163.052803794637</v>
+        <v>1005.430107765823</v>
       </c>
       <c r="N43" t="n">
-        <v>1163.052803794637</v>
+        <v>826.7320022587398</v>
       </c>
       <c r="O43" t="n">
-        <v>1161.481467112728</v>
+        <v>570.2646499020598</v>
       </c>
       <c r="P43" t="n">
-        <v>843.8998519939179</v>
+        <v>252.6830347832499</v>
       </c>
       <c r="Q43" t="n">
-        <v>466.1220742155024</v>
+        <v>88.34429643772452</v>
       </c>
       <c r="R43" t="n">
         <v>88.34429643772452</v>
@@ -7615,22 +7615,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>29.92</v>
+        <v>130.8290456423631</v>
       </c>
       <c r="C44" t="n">
-        <v>29.92</v>
+        <v>130.8290456423631</v>
       </c>
       <c r="D44" t="n">
-        <v>29.92</v>
+        <v>130.8290456423631</v>
       </c>
       <c r="E44" t="n">
-        <v>29.92</v>
+        <v>130.8290456423631</v>
       </c>
       <c r="F44" t="n">
-        <v>29.92</v>
+        <v>130.8290456423631</v>
       </c>
       <c r="G44" t="n">
-        <v>29.92</v>
+        <v>130.8290456423631</v>
       </c>
       <c r="H44" t="n">
         <v>29.92</v>
@@ -7639,22 +7639,22 @@
         <v>29.92</v>
       </c>
       <c r="J44" t="n">
-        <v>400.180000000263</v>
+        <v>119.1959849731395</v>
       </c>
       <c r="K44" t="n">
-        <v>585.976737638454</v>
+        <v>304.9927226113305</v>
       </c>
       <c r="L44" t="n">
-        <v>816.4740199500117</v>
+        <v>578.9268279130014</v>
       </c>
       <c r="M44" t="n">
-        <v>1109.691587554807</v>
+        <v>949.1868279132643</v>
       </c>
       <c r="N44" t="n">
-        <v>1109.691587554807</v>
+        <v>949.1868279132643</v>
       </c>
       <c r="O44" t="n">
-        <v>1286.24475964128</v>
+        <v>1125.739999999737</v>
       </c>
       <c r="P44" t="n">
         <v>1496</v>
@@ -7675,16 +7675,16 @@
         <v>846.1814284698353</v>
       </c>
       <c r="V44" t="n">
-        <v>681.0869792339549</v>
+        <v>505.9278687053667</v>
       </c>
       <c r="W44" t="n">
-        <v>332.2248822835028</v>
+        <v>157.0657717549146</v>
       </c>
       <c r="X44" t="n">
-        <v>29.92</v>
+        <v>130.8290456423631</v>
       </c>
       <c r="Y44" t="n">
-        <v>29.92</v>
+        <v>130.8290456423631</v>
       </c>
     </row>
     <row r="45">
@@ -7718,19 +7718,19 @@
         <v>29.92</v>
       </c>
       <c r="J45" t="n">
-        <v>227.711345930016</v>
+        <v>29.92</v>
       </c>
       <c r="K45" t="n">
-        <v>543.0996394772296</v>
+        <v>345.3082935472136</v>
       </c>
       <c r="L45" t="n">
-        <v>863.9779994927574</v>
+        <v>402.1357049717419</v>
       </c>
       <c r="M45" t="n">
-        <v>863.9779994927574</v>
+        <v>686.2310967146011</v>
       </c>
       <c r="N45" t="n">
-        <v>863.9779994927574</v>
+        <v>1022.767095190094</v>
       </c>
       <c r="O45" t="n">
         <v>1234.237999492757</v>
@@ -7739,7 +7739,7 @@
         <v>1496</v>
       </c>
       <c r="Q45" t="n">
-        <v>1493.589117731894</v>
+        <v>1496</v>
       </c>
       <c r="R45" t="n">
         <v>1286.253778366616</v>
@@ -7815,10 +7815,10 @@
         <v>570.2646499020595</v>
       </c>
       <c r="P46" t="n">
-        <v>466.1220742163788</v>
+        <v>252.6830347832496</v>
       </c>
       <c r="Q46" t="n">
-        <v>88.34429643772449</v>
+        <v>252.6830347832496</v>
       </c>
       <c r="R46" t="n">
         <v>88.34429643772449</v>
@@ -7964,19 +7964,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2405037325275146</v>
+        <v>374.2405037325275</v>
       </c>
       <c r="K2" t="n">
-        <v>321.8400703517588</v>
+        <v>242.0199542155221</v>
       </c>
       <c r="L2" t="n">
-        <v>309.2909949748743</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>472.2608914614128</v>
       </c>
       <c r="N2" t="n">
-        <v>762.9715555014377</v>
+        <v>404.0826666125488</v>
       </c>
       <c r="O2" t="n">
         <v>1.159015302735668</v>
@@ -7985,7 +7985,7 @@
         <v>315.3213213472141</v>
       </c>
       <c r="Q2" t="n">
-        <v>128.5418702571336</v>
+        <v>502.5418702571336</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8204,25 +8204,25 @@
         <v>374.2405037325275</v>
       </c>
       <c r="K5" t="n">
-        <v>321.8400703517588</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>235.5012052109776</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>472.2608914614128</v>
+        <v>846.2608914614127</v>
       </c>
       <c r="N5" t="n">
         <v>404.0826666125488</v>
       </c>
       <c r="O5" t="n">
-        <v>1.159015302735668</v>
+        <v>375.1590153027356</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>502.5418702571336</v>
+        <v>311.8831458198699</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8438,28 +8438,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2405037325275146</v>
+        <v>374.2405037325275</v>
       </c>
       <c r="K8" t="n">
-        <v>321.8400703517588</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>309.2909949748743</v>
+        <v>183.3412755627362</v>
       </c>
       <c r="M8" t="n">
-        <v>846.2608914614127</v>
+        <v>472.2608914614128</v>
       </c>
       <c r="N8" t="n">
         <v>404.0826666125488</v>
       </c>
       <c r="O8" t="n">
-        <v>1.159015302735668</v>
+        <v>375.1590153027356</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>428.7520804932368</v>
+        <v>502.5418702571336</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8675,19 +8675,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>467.3265276381908</v>
+        <v>467.326527638191</v>
       </c>
       <c r="L11" t="n">
-        <v>140.0167990402167</v>
+        <v>422.1744623115576</v>
       </c>
       <c r="M11" t="n">
-        <v>940.1988562855336</v>
+        <v>433.3459296003489</v>
       </c>
       <c r="N11" t="n">
-        <v>213.993772140187</v>
+        <v>868.993772140187</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -8912,19 +8912,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K14" t="n">
-        <v>467.326527638191</v>
+        <v>237.8153698971238</v>
       </c>
       <c r="L14" t="n">
-        <v>422.1744623115576</v>
+        <v>422.1744623115578</v>
       </c>
       <c r="M14" t="n">
-        <v>433.3459296003489</v>
+        <v>285.1988562855334</v>
       </c>
       <c r="N14" t="n">
-        <v>868.993772140187</v>
+        <v>213.993772140187</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -8933,7 +8933,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>13.49857879984722</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9152,25 +9152,25 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>467.326527638191</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>422.1744623115576</v>
+        <v>170.5050864162431</v>
       </c>
       <c r="M17" t="n">
-        <v>940.1988562855345</v>
+        <v>285.1988562855334</v>
       </c>
       <c r="N17" t="n">
-        <v>362.1408454550021</v>
+        <v>213.993772140187</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>476.6634625389175</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>443.1260198396775</v>
       </c>
       <c r="Q17" t="n">
-        <v>13.49857879984722</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9386,25 +9386,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>467.3265276381908</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>422.1744623115578</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>658.0411930141927</v>
+        <v>940.1988562855354</v>
       </c>
       <c r="N20" t="n">
-        <v>213.993772140187</v>
+        <v>331.8523530261527</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>476.6634625389185</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>443.1260198396784</v>
       </c>
       <c r="Q20" t="n">
         <v>13.49857879984722</v>
@@ -9623,19 +9623,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>467.3265276381908</v>
+        <v>467.326527638191</v>
       </c>
       <c r="L23" t="n">
-        <v>422.1744623115578</v>
+        <v>422.1744623115576</v>
       </c>
       <c r="M23" t="n">
-        <v>658.0411930141927</v>
+        <v>433.3459296003437</v>
       </c>
       <c r="N23" t="n">
-        <v>213.993772140187</v>
+        <v>868.9937721401925</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -9863,16 +9863,16 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
-        <v>237.8153698971238</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>422.1744623115578</v>
+        <v>4.989832208668531</v>
       </c>
       <c r="M26" t="n">
         <v>285.1988562855334</v>
       </c>
       <c r="N26" t="n">
-        <v>213.993772140187</v>
+        <v>868.9937721401998</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -10100,13 +10100,13 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>467.3265276381908</v>
       </c>
       <c r="L29" t="n">
-        <v>4.989832208661028</v>
+        <v>192.6633045704907</v>
       </c>
       <c r="M29" t="n">
-        <v>940.1988562855538</v>
+        <v>285.1988562855334</v>
       </c>
       <c r="N29" t="n">
         <v>213.993772140187</v>
@@ -10334,19 +10334,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>467.3265276381908</v>
+        <v>467.326527638191</v>
       </c>
       <c r="L32" t="n">
-        <v>140.0167990401842</v>
+        <v>422.1744623115576</v>
       </c>
       <c r="M32" t="n">
         <v>940.1988562855663</v>
       </c>
       <c r="N32" t="n">
-        <v>213.993772140187</v>
+        <v>362.1408454549699</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -10571,16 +10571,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>283.8222374009275</v>
       </c>
       <c r="K35" t="n">
-        <v>64.82713630648368</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>141.1744623115578</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>659.1988562855918</v>
+        <v>285.1988562855334</v>
       </c>
       <c r="N35" t="n">
         <v>213.993772140187</v>
@@ -10592,7 +10592,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>13.49857879984722</v>
+        <v>309.6779400170195</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10656,19 +10656,19 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>316.5985743187165</v>
       </c>
       <c r="M36" t="n">
-        <v>471.6948204301074</v>
+        <v>184.7297782656032</v>
       </c>
       <c r="N36" t="n">
-        <v>145.473175175903</v>
+        <v>485.4085271713503</v>
       </c>
       <c r="O36" t="n">
-        <v>307.1604212273249</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>219.1507118405495</v>
+        <v>156.7422489182151</v>
       </c>
       <c r="Q36" t="n">
         <v>17.27519534353338</v>
@@ -10887,25 +10887,25 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J39" t="n">
-        <v>227.4647419277884</v>
+        <v>27.675503614641</v>
       </c>
       <c r="K39" t="n">
         <v>295.8802408630135</v>
       </c>
       <c r="L39" t="n">
-        <v>266.7181298898984</v>
+        <v>316.5985743187511</v>
       </c>
       <c r="M39" t="n">
         <v>184.7297782656032</v>
       </c>
       <c r="N39" t="n">
-        <v>145.473175175903</v>
+        <v>485.4085271713503</v>
       </c>
       <c r="O39" t="n">
-        <v>327.4073335019309</v>
+        <v>327.4073335020238</v>
       </c>
       <c r="P39" t="n">
-        <v>219.1507118405495</v>
+        <v>29.12415372930433</v>
       </c>
       <c r="Q39" t="n">
         <v>17.27519534353338</v>
@@ -11048,10 +11048,10 @@
         <v>283.8222374010075</v>
       </c>
       <c r="K41" t="n">
-        <v>186.326527638191</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>109.8528335789012</v>
+        <v>100.5158986780375</v>
       </c>
       <c r="M41" t="n">
         <v>285.1988562855334</v>
@@ -11060,7 +11060,7 @@
         <v>213.993772140187</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>195.6634625390549</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
@@ -11124,25 +11124,25 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J42" t="n">
-        <v>227.4647419277884</v>
+        <v>27.675503614641</v>
       </c>
       <c r="K42" t="n">
-        <v>295.8802408630135</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>266.7181298898984</v>
+        <v>316.5985743186583</v>
       </c>
       <c r="M42" t="n">
-        <v>184.7297782656032</v>
+        <v>471.6948204301074</v>
       </c>
       <c r="N42" t="n">
-        <v>145.473175175903</v>
+        <v>485.4085271713503</v>
       </c>
       <c r="O42" t="n">
         <v>327.4073335019309</v>
       </c>
       <c r="P42" t="n">
-        <v>219.1507118405495</v>
+        <v>38.03935242799921</v>
       </c>
       <c r="Q42" t="n">
         <v>17.27519534353338</v>
@@ -11282,16 +11282,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>283.8222374011348</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>43.87557877789203</v>
       </c>
       <c r="M44" t="n">
-        <v>581.3782175024983</v>
+        <v>659.1988562857991</v>
       </c>
       <c r="N44" t="n">
         <v>213.993772140187</v>
@@ -11300,7 +11300,7 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>162.126019839942</v>
       </c>
       <c r="Q44" t="n">
         <v>13.49857879984722</v>
@@ -11361,22 +11361,22 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J45" t="n">
-        <v>227.4647419277884</v>
+        <v>27.675503614641</v>
       </c>
       <c r="K45" t="n">
         <v>295.8802408630135</v>
       </c>
       <c r="L45" t="n">
-        <v>266.7181298898984</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>184.7297782656032</v>
+        <v>471.6948204301074</v>
       </c>
       <c r="N45" t="n">
-        <v>145.473175175903</v>
+        <v>485.4085271713503</v>
       </c>
       <c r="O45" t="n">
-        <v>327.4073335019309</v>
+        <v>167.0143075450254</v>
       </c>
       <c r="P45" t="n">
         <v>219.1507118405495</v>
@@ -23223,25 +23223,25 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
         <v>0.6960849964949034</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -23417,7 +23417,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.850361477466578</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -23426,7 +23426,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.850361477466322</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -23511,13 +23511,13 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>0.6960849964951876</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6960849964951308</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -23663,13 +23663,13 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.850361477466379</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.850361477466322</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -23748,7 +23748,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>0.696084996495216</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
@@ -23763,7 +23763,7 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.6960849964949034</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
@@ -23943,7 +23943,7 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>0.6960849964949034</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -23985,7 +23985,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.696084996495216</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -24186,7 +24186,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>0.6960849964948983</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -24222,7 +24222,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6960849964951876</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
@@ -24423,7 +24423,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.696084996494875</v>
+        <v>0.6960849964948983</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -24611,13 +24611,13 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.850361477466322</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.85036147746635</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -24660,7 +24660,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.6960849964948983</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -24702,7 +24702,7 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>0.6960849964951308</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -24833,7 +24833,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>2.850361477466563</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -24854,7 +24854,7 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.850361477466322</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -25091,7 +25091,7 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>2.850361477455998</v>
+        <v>2.850361477458247</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -25134,7 +25134,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>3.300929810555617</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -25188,7 +25188,7 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>3.300929810555601</v>
       </c>
     </row>
     <row r="36">
@@ -25368,7 +25368,7 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>3.300929810555594</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -25407,7 +25407,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>3.300929810555601</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
@@ -25593,19 +25593,19 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>188.9993129555745</v>
+        <v>161.0849030909154</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>117.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>111.8896287080119</v>
       </c>
       <c r="G41" t="n">
         <v>109.2819954025941</v>
@@ -25644,13 +25644,13 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>168.2280170485541</v>
       </c>
       <c r="T41" t="n">
         <v>287.2171194170061</v>
       </c>
       <c r="U41" t="n">
-        <v>134.8640801520572</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -25781,25 +25781,25 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>32.15552979712345</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>123.8909392714024</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>176.9111244520127</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>252.3470555180231</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.422266424966665</v>
+        <v>214.7269154635279</v>
       </c>
       <c r="R43" t="n">
-        <v>29.84504601393797</v>
+        <v>403.8450460139379</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -25848,7 +25848,7 @@
         <v>109.2819954025941</v>
       </c>
       <c r="H44" t="n">
-        <v>99.89995518593948</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -25890,13 +25890,13 @@
         <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>173.4075194233023</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>273.3074746092418</v>
       </c>
       <c r="Y44" t="n">
         <v>218.3174326828064</v>
@@ -26030,13 +26030,13 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>211.3046490387979</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.422266424730196</v>
+        <v>377.422266425598</v>
       </c>
       <c r="R46" t="n">
-        <v>403.845046013938</v>
+        <v>241.1496950518681</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6518080.84626829</v>
+        <v>6518080.846268289</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7588446.086065989</v>
+        <v>7588446.086065988</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8658811.325863687</v>
+        <v>8658811.325863685</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9729176.565661386</v>
+        <v>9729176.565661384</v>
       </c>
     </row>
     <row r="11">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15892395.67724404</v>
+        <v>15892395.67724403</v>
       </c>
     </row>
   </sheetData>
@@ -26278,25 +26278,25 @@
         <v>1133439.336299335</v>
       </c>
       <c r="E2" t="n">
+        <v>1133327.900962274</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1133327.900962274</v>
+      </c>
+      <c r="G2" t="n">
         <v>1133327.900962275</v>
       </c>
-      <c r="F2" t="n">
+      <c r="H2" t="n">
         <v>1133327.900962275</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1133327.900962274</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1133327.900962274</v>
       </c>
       <c r="I2" t="n">
         <v>1133327.900962274</v>
       </c>
       <c r="J2" t="n">
+        <v>1133327.900962274</v>
+      </c>
+      <c r="K2" t="n">
         <v>1133327.900962275</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1133327.900962274</v>
       </c>
       <c r="L2" t="n">
         <v>1133327.900962275</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>602419.1762101187</v>
+        <v>602219.8615549038</v>
       </c>
       <c r="C4" t="n">
-        <v>600410.2540226299</v>
+        <v>600210.9393674152</v>
       </c>
       <c r="D4" t="n">
-        <v>598398.6066068059</v>
+        <v>598199.291951591</v>
       </c>
       <c r="E4" t="n">
-        <v>508463.6174685807</v>
+        <v>508269.4590428486</v>
       </c>
       <c r="F4" t="n">
-        <v>506794.9519687437</v>
+        <v>506600.7935430115</v>
       </c>
       <c r="G4" t="n">
-        <v>505123.9837731232</v>
+        <v>504929.8253473911</v>
       </c>
       <c r="H4" t="n">
-        <v>503450.6963689994</v>
+        <v>503256.5379432672</v>
       </c>
       <c r="I4" t="n">
-        <v>501775.0730285004</v>
+        <v>501580.9146027682</v>
       </c>
       <c r="J4" t="n">
-        <v>500097.0968045217</v>
+        <v>499902.9383787896</v>
       </c>
       <c r="K4" t="n">
-        <v>498416.75052655</v>
+        <v>498222.5921008177</v>
       </c>
       <c r="L4" t="n">
-        <v>496734.0167963755</v>
+        <v>496539.8583706433</v>
       </c>
       <c r="M4" t="n">
-        <v>522490.4615842147</v>
+        <v>522371.0444804642</v>
       </c>
       <c r="N4" t="n">
-        <v>520523.3308731495</v>
+        <v>520403.913769399</v>
       </c>
       <c r="O4" t="n">
-        <v>447790.3844155932</v>
+        <v>447670.9673118427</v>
       </c>
       <c r="P4" t="n">
-        <v>446122.6297523478</v>
+        <v>446003.2126485973</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>241331.7600892164</v>
+        <v>241531.0747444316</v>
       </c>
       <c r="C6" t="n">
-        <v>474438.6822767049</v>
+        <v>474637.9969319199</v>
       </c>
       <c r="D6" t="n">
-        <v>476450.3296925294</v>
+        <v>476649.6443477438</v>
       </c>
       <c r="E6" t="n">
-        <v>-62265.32750630597</v>
+        <v>-62071.16908057427</v>
       </c>
       <c r="F6" t="n">
-        <v>551890.3379935308</v>
+        <v>552084.4964192625</v>
       </c>
       <c r="G6" t="n">
-        <v>553561.306189151</v>
+        <v>553755.4646148834</v>
       </c>
       <c r="H6" t="n">
-        <v>555234.5935932745</v>
+        <v>555428.7520190072</v>
       </c>
       <c r="I6" t="n">
-        <v>556910.2169337734</v>
+        <v>557104.3753595061</v>
       </c>
       <c r="J6" t="n">
-        <v>171740.1931577532</v>
+        <v>171934.3515834845</v>
       </c>
       <c r="K6" t="n">
-        <v>560268.5394357243</v>
+        <v>560462.697861457</v>
       </c>
       <c r="L6" t="n">
-        <v>561951.2731658993</v>
+        <v>562145.4315916311</v>
       </c>
       <c r="M6" t="n">
-        <v>484197.2031034924</v>
+        <v>484316.6202072431</v>
       </c>
       <c r="N6" t="n">
-        <v>548564.3338145567</v>
+        <v>548683.7509183066</v>
       </c>
       <c r="O6" t="n">
-        <v>340665.189114681</v>
+        <v>340784.606218431</v>
       </c>
       <c r="P6" t="n">
-        <v>514332.9437779253</v>
+        <v>514452.3608816754</v>
       </c>
     </row>
   </sheetData>
@@ -26984,10 +26984,10 @@
         <v>319</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>-0</v>
@@ -27451,10 +27451,10 @@
         <v>400</v>
       </c>
       <c r="H2" t="n">
-        <v>398.2013121321735</v>
+        <v>400</v>
       </c>
       <c r="I2" t="n">
-        <v>134.2726973711268</v>
+        <v>132.4740095033003</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27527,13 +27527,13 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>325.5201396486123</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>330.0491815260438</v>
+        <v>321.0783873143264</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>209.5726123064429</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27560,22 +27560,22 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>159.6519859716246</v>
+        <v>400</v>
       </c>
       <c r="S3" t="n">
         <v>400</v>
       </c>
       <c r="T3" t="n">
-        <v>30.47344446279683</v>
+        <v>400</v>
       </c>
       <c r="U3" t="n">
-        <v>183.8400581130405</v>
+        <v>400</v>
       </c>
       <c r="V3" t="n">
-        <v>400</v>
+        <v>40.51066719152016</v>
       </c>
       <c r="W3" t="n">
-        <v>400</v>
+        <v>58.37314290982852</v>
       </c>
       <c r="X3" t="n">
         <v>400</v>
@@ -27594,7 +27594,7 @@
         <v>400</v>
       </c>
       <c r="C4" t="n">
-        <v>318.4806470903476</v>
+        <v>400</v>
       </c>
       <c r="D4" t="n">
         <v>400</v>
@@ -27615,13 +27615,13 @@
         <v>171.1020457840527</v>
       </c>
       <c r="J4" t="n">
-        <v>396.2647849014816</v>
+        <v>289.8761917713253</v>
       </c>
       <c r="K4" t="n">
         <v>267.1509377355693</v>
       </c>
       <c r="L4" t="n">
-        <v>396.2015953708939</v>
+        <v>400</v>
       </c>
       <c r="M4" t="n">
         <v>400</v>
@@ -27654,10 +27654,10 @@
         <v>199.1703102162162</v>
       </c>
       <c r="W4" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X4" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
         <v>400</v>
@@ -27688,7 +27688,7 @@
         <v>400</v>
       </c>
       <c r="H5" t="n">
-        <v>400</v>
+        <v>398.2013121321735</v>
       </c>
       <c r="I5" t="n">
         <v>134.2726973711268</v>
@@ -27721,7 +27721,7 @@
         <v>225.120779732817</v>
       </c>
       <c r="S5" t="n">
-        <v>398.2013121321733</v>
+        <v>400</v>
       </c>
       <c r="T5" t="n">
         <v>400</v>
@@ -27749,10 +27749,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>84.04934533286502</v>
+        <v>10.55655664632661</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
         <v>347.9376868977026</v>
@@ -27770,7 +27770,7 @@
         <v>330.0491815260438</v>
       </c>
       <c r="I6" t="n">
-        <v>209.5726123064429</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27797,7 +27797,7 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>400</v>
+        <v>302.1027491020745</v>
       </c>
       <c r="S6" t="n">
         <v>400</v>
@@ -27815,10 +27815,10 @@
         <v>400</v>
       </c>
       <c r="X6" t="n">
-        <v>400</v>
+        <v>45.86273944538755</v>
       </c>
       <c r="Y6" t="n">
-        <v>25.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="7">
@@ -27834,28 +27834,28 @@
         <v>400</v>
       </c>
       <c r="D7" t="n">
-        <v>400</v>
+        <v>295.7112478557377</v>
       </c>
       <c r="E7" t="n">
-        <v>400</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F7" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G7" t="n">
-        <v>400</v>
+        <v>244.8599384153005</v>
       </c>
       <c r="H7" t="n">
-        <v>400</v>
+        <v>227.1357818393235</v>
       </c>
       <c r="I7" t="n">
-        <v>400</v>
+        <v>171.1020457840527</v>
       </c>
       <c r="J7" t="n">
         <v>22.26478490148153</v>
       </c>
       <c r="K7" t="n">
-        <v>368.9819193021434</v>
+        <v>267.1509377355693</v>
       </c>
       <c r="L7" t="n">
         <v>396.2015953708939</v>
@@ -27879,22 +27879,22 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>359.1680042930194</v>
+        <v>400</v>
       </c>
       <c r="T7" t="n">
-        <v>209.2386648669134</v>
+        <v>400</v>
       </c>
       <c r="U7" t="n">
-        <v>150.9483584875727</v>
+        <v>400</v>
       </c>
       <c r="V7" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W7" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X7" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y7" t="n">
         <v>400</v>
@@ -27955,10 +27955,10 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>223.3220918649904</v>
+        <v>225.120779732817</v>
       </c>
       <c r="S8" t="n">
-        <v>400</v>
+        <v>398.2013121321733</v>
       </c>
       <c r="T8" t="n">
         <v>400</v>
@@ -27986,10 +27986,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
         <v>347.9376868977026</v>
@@ -28007,7 +28007,7 @@
         <v>330.0491815260438</v>
       </c>
       <c r="I9" t="n">
-        <v>209.5726123064429</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28031,19 +28031,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>73.49278868653825</v>
+        <v>145.073529241423</v>
       </c>
       <c r="R9" t="n">
-        <v>400</v>
+        <v>159.6519859716246</v>
       </c>
       <c r="S9" t="n">
-        <v>400</v>
+        <v>88.48881128536601</v>
       </c>
       <c r="T9" t="n">
-        <v>400</v>
+        <v>30.47344446279683</v>
       </c>
       <c r="U9" t="n">
-        <v>400</v>
+        <v>350.2777175862515</v>
       </c>
       <c r="V9" t="n">
         <v>400</v>
@@ -28055,7 +28055,7 @@
         <v>400</v>
       </c>
       <c r="Y9" t="n">
-        <v>25.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="10">
@@ -28068,16 +28068,16 @@
         <v>287.1138003370787</v>
       </c>
       <c r="C10" t="n">
-        <v>306.0958044180808</v>
+        <v>400</v>
       </c>
       <c r="D10" t="n">
         <v>285.5362180555555</v>
       </c>
       <c r="E10" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F10" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G10" t="n">
         <v>244.8599384153005</v>
@@ -28089,10 +28089,10 @@
         <v>171.1020457840527</v>
       </c>
       <c r="J10" t="n">
-        <v>396.2647849014816</v>
+        <v>381.334747521778</v>
       </c>
       <c r="K10" t="n">
-        <v>400</v>
+        <v>267.1509377355693</v>
       </c>
       <c r="L10" t="n">
         <v>396.2015953708939</v>
@@ -28119,7 +28119,7 @@
         <v>359.1680042930194</v>
       </c>
       <c r="T10" t="n">
-        <v>400</v>
+        <v>209.2386648669134</v>
       </c>
       <c r="U10" t="n">
         <v>150.9483584875727</v>
@@ -28229,16 +28229,16 @@
         <v>319</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="E12" t="n">
         <v>319</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="G12" t="n">
-        <v>96.05772723972433</v>
+        <v>319</v>
       </c>
       <c r="H12" t="n">
         <v>319</v>
@@ -28268,16 +28268,16 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>72.31352924142297</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>319</v>
+        <v>168.3712564811473</v>
       </c>
       <c r="T12" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
         <v>319</v>
@@ -28286,10 +28286,10 @@
         <v>319</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="X12" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>319</v>
@@ -28463,10 +28463,10 @@
         <v>319</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="D15" t="n">
-        <v>96.0577272397245</v>
+        <v>319</v>
       </c>
       <c r="E15" t="n">
         <v>319</v>
@@ -28517,13 +28517,13 @@
         <v>319</v>
       </c>
       <c r="U15" t="n">
-        <v>319</v>
+        <v>96.05772723972433</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -28697,7 +28697,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>319</v>
+        <v>96.05772723972427</v>
       </c>
       <c r="C18" t="n">
         <v>319</v>
@@ -28757,7 +28757,7 @@
         <v>319</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
@@ -28766,7 +28766,7 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>96.05772723972444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -28934,10 +28934,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>96.0577272397245</v>
+        <v>319</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -28946,13 +28946,13 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
         <v>319</v>
       </c>
       <c r="H21" t="n">
-        <v>319</v>
+        <v>96.05772723972422</v>
       </c>
       <c r="I21" t="n">
         <v>189.9476123064429</v>
@@ -29174,7 +29174,7 @@
         <v>319</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>96.05772723972427</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -29183,7 +29183,7 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>96.0577272397243</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>319</v>
@@ -29417,16 +29417,16 @@
         <v>319</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="G27" t="n">
-        <v>96.05772723972444</v>
+        <v>319</v>
       </c>
       <c r="H27" t="n">
-        <v>319</v>
+        <v>96.05772723972461</v>
       </c>
       <c r="I27" t="n">
         <v>189.9476123064429</v>
@@ -29459,7 +29459,7 @@
         <v>319</v>
       </c>
       <c r="S27" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
         <v>319</v>
@@ -29468,16 +29468,16 @@
         <v>319</v>
       </c>
       <c r="V27" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
         <v>319</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
     </row>
     <row r="28">
@@ -29651,7 +29651,7 @@
         <v>319</v>
       </c>
       <c r="D30" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -29666,7 +29666,7 @@
         <v>319</v>
       </c>
       <c r="I30" t="n">
-        <v>189.9476123064429</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -29705,16 +29705,16 @@
         <v>319</v>
       </c>
       <c r="V30" t="n">
-        <v>96.0577272397245</v>
+        <v>319</v>
       </c>
       <c r="W30" t="n">
         <v>319</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="Y30" t="n">
-        <v>319</v>
+        <v>286.0053395461672</v>
       </c>
     </row>
     <row r="31">
@@ -29927,31 +29927,31 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>72.31352924142297</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>319</v>
+        <v>168.3712564811474</v>
       </c>
       <c r="U33" t="n">
         <v>319</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="Y33" t="n">
-        <v>96.05772723972444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -29961,10 +29961,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>319.0000000000103</v>
+        <v>319</v>
       </c>
       <c r="C34" t="n">
-        <v>319</v>
+        <v>319.0000000000082</v>
       </c>
       <c r="D34" t="n">
         <v>319</v>
@@ -30119,13 +30119,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>10.55655664632661</v>
+        <v>10.55655664626832</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E36" t="n">
         <v>342.6720972219126</v>
@@ -30137,7 +30137,7 @@
         <v>324.9501396486123</v>
       </c>
       <c r="H36" t="n">
-        <v>324.5441815260438</v>
+        <v>212.5064591452776</v>
       </c>
       <c r="I36" t="n">
         <v>189.9476123064429</v>
@@ -30185,10 +30185,10 @@
         <v>397</v>
       </c>
       <c r="X36" t="n">
-        <v>397</v>
+        <v>45.86273944532931</v>
       </c>
       <c r="Y36" t="n">
-        <v>271.2540091738027</v>
+        <v>25.39139276607611</v>
       </c>
     </row>
     <row r="37">
@@ -30201,22 +30201,22 @@
         <v>397</v>
       </c>
       <c r="C37" t="n">
+        <v>272.7252466480447</v>
+      </c>
+      <c r="D37" t="n">
+        <v>285.5362180555555</v>
+      </c>
+      <c r="E37" t="n">
+        <v>280.9809048369565</v>
+      </c>
+      <c r="F37" t="n">
         <v>397</v>
       </c>
-      <c r="D37" t="n">
-        <v>397</v>
-      </c>
-      <c r="E37" t="n">
-        <v>349.4188900942756</v>
-      </c>
-      <c r="F37" t="n">
-        <v>274.3828559677419</v>
-      </c>
       <c r="G37" t="n">
-        <v>397</v>
+        <v>244.3820695628415</v>
       </c>
       <c r="H37" t="n">
-        <v>397</v>
+        <v>278.4403193339402</v>
       </c>
       <c r="I37" t="n">
         <v>156.7312261119215</v>
@@ -30225,10 +30225,10 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
+        <v>211.6312656044217</v>
+      </c>
+      <c r="L37" t="n">
         <v>397</v>
-      </c>
-      <c r="L37" t="n">
-        <v>325.1555297971234</v>
       </c>
       <c r="M37" t="n">
         <v>397</v>
@@ -30255,16 +30255,16 @@
         <v>207.1968615882249</v>
       </c>
       <c r="U37" t="n">
-        <v>150.9222929138022</v>
+        <v>397</v>
       </c>
       <c r="V37" t="n">
         <v>199.1703102162162</v>
       </c>
       <c r="W37" t="n">
-        <v>226.3728098387097</v>
+        <v>397</v>
       </c>
       <c r="X37" t="n">
-        <v>247.4436454301076</v>
+        <v>397</v>
       </c>
       <c r="Y37" t="n">
         <v>397</v>
@@ -30359,16 +30359,16 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C39" t="n">
-        <v>361.0999124455193</v>
+        <v>182.5623487335918</v>
       </c>
       <c r="D39" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
         <v>324.9501396486123</v>
@@ -30377,7 +30377,7 @@
         <v>324.5441815260438</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>189.9476123064429</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -30401,10 +30401,10 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>72.31352924142297</v>
       </c>
       <c r="R39" t="n">
-        <v>177.8084583890038</v>
+        <v>397</v>
       </c>
       <c r="S39" t="n">
         <v>397</v>
@@ -30413,10 +30413,10 @@
         <v>397</v>
       </c>
       <c r="U39" t="n">
-        <v>26.1584257979226</v>
+        <v>397</v>
       </c>
       <c r="V39" t="n">
-        <v>40.51066719152016</v>
+        <v>397</v>
       </c>
       <c r="W39" t="n">
         <v>397</v>
@@ -30447,10 +30447,10 @@
         <v>280.9809048369565</v>
       </c>
       <c r="F40" t="n">
-        <v>274.3828559677419</v>
+        <v>397</v>
       </c>
       <c r="G40" t="n">
-        <v>397</v>
+        <v>244.3820695628415</v>
       </c>
       <c r="H40" t="n">
         <v>397</v>
@@ -30459,7 +30459,7 @@
         <v>397</v>
       </c>
       <c r="J40" t="n">
-        <v>159.4038561464489</v>
+        <v>362.4794570327219</v>
       </c>
       <c r="K40" t="n">
         <v>211.6312656044217</v>
@@ -30486,7 +30486,7 @@
         <v>397</v>
       </c>
       <c r="S40" t="n">
-        <v>350.8400534733473</v>
+        <v>375.5949287757585</v>
       </c>
       <c r="T40" t="n">
         <v>207.1968615882249</v>
@@ -30495,7 +30495,7 @@
         <v>150.9222929138022</v>
       </c>
       <c r="V40" t="n">
-        <v>397</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W40" t="n">
         <v>226.3728098387097</v>
@@ -30611,7 +30611,7 @@
         <v>293</v>
       </c>
       <c r="H42" t="n">
-        <v>293</v>
+        <v>290.6132265545749</v>
       </c>
       <c r="I42" t="n">
         <v>189.9476123064429</v>
@@ -30638,7 +30638,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>69.92675579599782</v>
+        <v>72.31352924142297</v>
       </c>
       <c r="R42" t="n">
         <v>293</v>
@@ -30875,10 +30875,10 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>69.92675579599782</v>
+        <v>72.31352924142297</v>
       </c>
       <c r="R45" t="n">
-        <v>293</v>
+        <v>290.6132265545748</v>
       </c>
       <c r="S45" t="n">
         <v>293</v>
@@ -34743,19 +34743,19 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="K2" t="n">
-        <v>374</v>
+        <v>294.1798838637633</v>
       </c>
       <c r="L2" t="n">
-        <v>373.9999999999999</v>
+        <v>64.70900502512563</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>358.888888888889</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -34764,7 +34764,7 @@
         <v>374</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34880,7 +34880,7 @@
         <v>112.8861996629213</v>
       </c>
       <c r="C4" t="n">
-        <v>45.75540044230294</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D4" t="n">
         <v>114.4637819444445</v>
@@ -34901,13 +34901,13 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>374</v>
+        <v>267.6114068698438</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3.798404629106074</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -34940,10 +34940,10 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X4" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>112.5346471505376</v>
@@ -34983,25 +34983,25 @@
         <v>374</v>
       </c>
       <c r="K5" t="n">
-        <v>373.9999999999999</v>
+        <v>52.15992964824119</v>
       </c>
       <c r="L5" t="n">
-        <v>300.2102102361032</v>
+        <v>64.70900502512563</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="P5" t="n">
         <v>58.67867865278593</v>
       </c>
       <c r="Q5" t="n">
-        <v>374</v>
+        <v>183.3412755627363</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35120,28 +35120,28 @@
         <v>127.2747533519553</v>
       </c>
       <c r="D7" t="n">
-        <v>114.4637819444445</v>
+        <v>10.17502980018224</v>
       </c>
       <c r="E7" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>155.1400615846995</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>172.8642181606765</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>228.8979542159473</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>101.830981566574</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -35165,22 +35165,22 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>40.83199570698065</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>190.7613351330866</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>249.0516415124273</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y7" t="n">
         <v>112.5346471505376</v>
@@ -35217,28 +35217,28 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="K8" t="n">
+        <v>52.15992964824119</v>
+      </c>
+      <c r="L8" t="n">
+        <v>248.0502805878618</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
         <v>374</v>
-      </c>
-      <c r="L8" t="n">
-        <v>373.9999999999999</v>
-      </c>
-      <c r="M8" t="n">
-        <v>374</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>58.67867865278593</v>
       </c>
       <c r="Q8" t="n">
-        <v>300.2102102361032</v>
+        <v>374</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35354,16 +35354,16 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>33.37055777003616</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -35375,10 +35375,10 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>374</v>
+        <v>359.0699626202965</v>
       </c>
       <c r="K10" t="n">
-        <v>132.8490622644307</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -35405,7 +35405,7 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>190.7613351330866</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -35454,19 +35454,19 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>520.4824991852875</v>
+        <v>90.1777625991308</v>
       </c>
       <c r="K11" t="n">
+        <v>655</v>
+      </c>
+      <c r="L11" t="n">
         <v>654.9999999999999</v>
       </c>
-      <c r="L11" t="n">
-        <v>372.8423367286589</v>
-      </c>
       <c r="M11" t="n">
+        <v>148.1470733148155</v>
+      </c>
+      <c r="N11" t="n">
         <v>655.0000000000001</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>178.3365374610834</v>
@@ -35615,7 +35615,7 @@
         <v>330.5205429673709</v>
       </c>
       <c r="K13" t="n">
-        <v>107.3687343955783</v>
+        <v>107.3687343955782</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -35691,19 +35691,19 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>90.1777625991308</v>
+        <v>520.4824991852875</v>
       </c>
       <c r="K14" t="n">
+        <v>425.4888422589328</v>
+      </c>
+      <c r="L14" t="n">
         <v>655</v>
       </c>
-      <c r="L14" t="n">
-        <v>654.9999999999999</v>
-      </c>
       <c r="M14" t="n">
-        <v>148.1470733148155</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>655.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>178.3365374610834</v>
@@ -35712,7 +35712,7 @@
         <v>211.8739801603236</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>602.3534944697265</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35852,7 +35852,7 @@
         <v>330.5205429673709</v>
       </c>
       <c r="K16" t="n">
-        <v>107.3687343955783</v>
+        <v>107.3687343955782</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -35931,25 +35931,25 @@
         <v>90.1777625991308</v>
       </c>
       <c r="K17" t="n">
-        <v>655</v>
+        <v>187.673472361809</v>
       </c>
       <c r="L17" t="n">
-        <v>654.9999999999999</v>
+        <v>403.3306241046854</v>
       </c>
       <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
         <v>655.000000000001</v>
       </c>
-      <c r="N17" t="n">
-        <v>148.1470733148151</v>
-      </c>
-      <c r="O17" t="n">
-        <v>178.3365374610834</v>
-      </c>
       <c r="P17" t="n">
-        <v>211.8739801603236</v>
+        <v>655.000000000001</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>602.3534944697265</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36165,25 +36165,25 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>520.4824991852875</v>
+        <v>90.1777625991308</v>
       </c>
       <c r="K20" t="n">
-        <v>654.9999999999999</v>
+        <v>187.673472361809</v>
       </c>
       <c r="L20" t="n">
-        <v>655</v>
+        <v>232.8255376884423</v>
       </c>
       <c r="M20" t="n">
-        <v>372.8423367286592</v>
+        <v>655.0000000000019</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>117.8585808859657</v>
       </c>
       <c r="O20" t="n">
-        <v>178.3365374610834</v>
+        <v>655.0000000000019</v>
       </c>
       <c r="P20" t="n">
-        <v>211.8739801603236</v>
+        <v>655.0000000000019</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -36402,19 +36402,19 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>520.4824991852875</v>
+        <v>90.1777625991308</v>
       </c>
       <c r="K23" t="n">
+        <v>655</v>
+      </c>
+      <c r="L23" t="n">
         <v>654.9999999999999</v>
       </c>
-      <c r="L23" t="n">
-        <v>655</v>
-      </c>
       <c r="M23" t="n">
-        <v>372.8423367286592</v>
+        <v>148.1470733148103</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>655.0000000000056</v>
       </c>
       <c r="O23" t="n">
         <v>178.3365374610834</v>
@@ -36642,16 +36642,16 @@
         <v>520.4824991852875</v>
       </c>
       <c r="K26" t="n">
-        <v>425.4888422589328</v>
+        <v>187.6734723618091</v>
       </c>
       <c r="L26" t="n">
-        <v>655</v>
+        <v>237.8153698971107</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>655.0000000000128</v>
       </c>
       <c r="O26" t="n">
         <v>178.3365374610834</v>
@@ -36800,7 +36800,7 @@
         <v>330.5205429673709</v>
       </c>
       <c r="K28" t="n">
-        <v>107.3687343955783</v>
+        <v>107.3687343955782</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -36879,13 +36879,13 @@
         <v>520.4824991852875</v>
       </c>
       <c r="K29" t="n">
-        <v>187.6734723618091</v>
+        <v>654.9999999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>237.8153698971032</v>
+        <v>425.4888422589329</v>
       </c>
       <c r="M29" t="n">
-        <v>655.0000000000203</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -37037,7 +37037,7 @@
         <v>330.5205429673709</v>
       </c>
       <c r="K31" t="n">
-        <v>107.3687343955782</v>
+        <v>107.3687343955783</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -37113,19 +37113,19 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>520.4824991852875</v>
+        <v>90.1777625991308</v>
       </c>
       <c r="K32" t="n">
+        <v>655</v>
+      </c>
+      <c r="L32" t="n">
         <v>654.9999999999999</v>
-      </c>
-      <c r="L32" t="n">
-        <v>372.8423367286264</v>
       </c>
       <c r="M32" t="n">
         <v>655.0000000000329</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>148.1470733147829</v>
       </c>
       <c r="O32" t="n">
         <v>178.3365374610834</v>
@@ -37247,10 +37247,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>31.88619966293162</v>
+        <v>31.88619966292134</v>
       </c>
       <c r="C34" t="n">
-        <v>46.27475335195533</v>
+        <v>46.27475335196356</v>
       </c>
       <c r="D34" t="n">
         <v>33.46378194444452</v>
@@ -37350,16 +37350,16 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>90.1777625991308</v>
+        <v>374.0000000000583</v>
       </c>
       <c r="K35" t="n">
-        <v>252.5006086682927</v>
+        <v>187.673472361809</v>
       </c>
       <c r="L35" t="n">
-        <v>374</v>
+        <v>232.8255376884422</v>
       </c>
       <c r="M35" t="n">
-        <v>374.0000000000583</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -37371,7 +37371,7 @@
         <v>211.8739801603236</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>296.1793612171723</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37435,19 +37435,19 @@
         <v>318.5740338860743</v>
       </c>
       <c r="L36" t="n">
-        <v>57.40142568134173</v>
+        <v>374.0000000000583</v>
       </c>
       <c r="M36" t="n">
-        <v>286.9650421645043</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>339.9353519954473</v>
       </c>
       <c r="O36" t="n">
-        <v>353.753087725394</v>
+        <v>46.59266649806909</v>
       </c>
       <c r="P36" t="n">
-        <v>264.4060611184268</v>
+        <v>201.9975981960925</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -37487,22 +37487,22 @@
         <v>109.8861996629213</v>
       </c>
       <c r="C37" t="n">
-        <v>124.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>111.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>68.43798525731901</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>122.6171440322581</v>
       </c>
       <c r="G37" t="n">
-        <v>152.6179304371585</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>174.1129066852666</v>
+        <v>55.5532260192068</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
@@ -37511,10 +37511,10 @@
         <v>11.52054296737091</v>
       </c>
       <c r="K37" t="n">
-        <v>185.3687343955783</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>71.84447020287656</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -37541,16 +37541,16 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>246.0777070861978</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>170.6271901612903</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>149.5563545698924</v>
       </c>
       <c r="Y37" t="n">
         <v>109.5346471505376</v>
@@ -37666,25 +37666,25 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>199.7892383131474</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
         <v>318.5740338860743</v>
       </c>
       <c r="L39" t="n">
-        <v>324.1195555712401</v>
+        <v>374.0000000000928</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>339.9353519954473</v>
       </c>
       <c r="O39" t="n">
-        <v>374</v>
+        <v>374.0000000000928</v>
       </c>
       <c r="P39" t="n">
-        <v>264.4060611184268</v>
+        <v>74.37950300718168</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -37733,10 +37733,10 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>122.6171440322581</v>
       </c>
       <c r="G40" t="n">
-        <v>152.6179304371585</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
         <v>174.1129066852666</v>
@@ -37745,7 +37745,7 @@
         <v>240.2687738880785</v>
       </c>
       <c r="J40" t="n">
-        <v>170.9243991138198</v>
+        <v>374.0000000000928</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -37772,7 +37772,7 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>24.75487530241127</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -37781,7 +37781,7 @@
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>197.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
         <v>0</v>
@@ -37827,10 +37827,10 @@
         <v>374.0000000001383</v>
       </c>
       <c r="K41" t="n">
-        <v>374.0000000000001</v>
+        <v>187.673472361809</v>
       </c>
       <c r="L41" t="n">
-        <v>342.6783712673434</v>
+        <v>333.3414363664797</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -37839,7 +37839,7 @@
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>178.3365374610834</v>
+        <v>374.0000000001383</v>
       </c>
       <c r="P41" t="n">
         <v>211.8739801603236</v>
@@ -37903,25 +37903,25 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>199.7892383131474</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>318.5740338860743</v>
+        <v>22.69379302306083</v>
       </c>
       <c r="L42" t="n">
-        <v>324.1195555712401</v>
+        <v>374</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>286.9650421645043</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>339.9353519954473</v>
       </c>
       <c r="O42" t="n">
         <v>374</v>
       </c>
       <c r="P42" t="n">
-        <v>264.4060611184268</v>
+        <v>83.29470170587656</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -38061,16 +38061,16 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
+        <v>90.1777625991308</v>
+      </c>
+      <c r="K44" t="n">
+        <v>187.673472361809</v>
+      </c>
+      <c r="L44" t="n">
+        <v>276.7011164663343</v>
+      </c>
+      <c r="M44" t="n">
         <v>374.0000000002656</v>
-      </c>
-      <c r="K44" t="n">
-        <v>187.6734723618091</v>
-      </c>
-      <c r="L44" t="n">
-        <v>232.8255376884422</v>
-      </c>
-      <c r="M44" t="n">
-        <v>296.1793612169649</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
@@ -38079,7 +38079,7 @@
         <v>178.3365374610834</v>
       </c>
       <c r="P44" t="n">
-        <v>211.8739801603236</v>
+        <v>374.0000000002656</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -38140,22 +38140,22 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>199.7892383131474</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
         <v>318.5740338860743</v>
       </c>
       <c r="L45" t="n">
-        <v>324.1195555712401</v>
+        <v>57.40142568134173</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>286.9650421645043</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>339.9353519954473</v>
       </c>
       <c r="O45" t="n">
-        <v>374</v>
+        <v>213.6069740430944</v>
       </c>
       <c r="P45" t="n">
         <v>264.4060611184268</v>
